--- a/artfynd/A 48499-2024 artfynd.xlsx
+++ b/artfynd/A 48499-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123238030</v>
+        <v>123225324</v>
       </c>
       <c r="B3" t="n">
         <v>57478</v>
@@ -816,24 +816,21 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478302</v>
+        <v>478477</v>
       </c>
       <c r="R3" t="n">
-        <v>6791004</v>
+        <v>6790674</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,6 +863,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Tretå hack mitt i avverkningsområdet där även gallring utförts utan att ha uppmärksammat spåren!</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -994,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123225324</v>
+        <v>123237971</v>
       </c>
       <c r="B5" t="n">
         <v>57478</v>
@@ -1027,25 +1029,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478477</v>
+        <v>478334</v>
       </c>
       <c r="R5" t="n">
-        <v>6790674</v>
+        <v>6790644</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1079,7 +1088,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Tretå hack mitt i avverkningsområdet där även gallring utförts utan att ha uppmärksammat spåren!</t>
+          <t>Trumning från två håll i pågånde avverkningsområde vilket utförs av Mellanskog!</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123237971</v>
+        <v>123222386</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1122,49 +1131,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478334</v>
+        <v>478251</v>
       </c>
       <c r="R6" t="n">
-        <v>6790644</v>
+        <v>6790651</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,7 +1195,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Trumning från två håll i pågånde avverkningsområde vilket utförs av Mellanskog!</t>
+          <t>Rikligt med garnlav i området. I alla riktningar sp långt man ser.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,10 +1222,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123222386</v>
+        <v>123225119</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,34 +1238,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478251</v>
+        <v>478467</v>
       </c>
       <c r="R7" t="n">
-        <v>6790651</v>
+        <v>6790672</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,11 +1303,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i området. I alla riktningar sp långt man ser.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,10 +1329,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123225119</v>
+        <v>123219384</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1348,39 +1345,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478467</v>
+        <v>478302</v>
       </c>
       <c r="R8" t="n">
-        <v>6790672</v>
+        <v>6791004</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,6 +1405,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,7 +1436,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123219384</v>
+        <v>123220031</v>
       </c>
       <c r="B9" t="n">
         <v>78766</v>
@@ -1479,10 +1476,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478302</v>
+        <v>478291</v>
       </c>
       <c r="R9" t="n">
-        <v>6791004</v>
+        <v>6790967</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1519,7 +1516,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav i en radie av ca 30 meter</t>
+          <t>Rikligt med garnlav i en radie av ca 30 meter. Tallar och granar med ålder mer än 150 år</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,10 +1543,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123220031</v>
+        <v>123220064</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>56078</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1562,34 +1559,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478291</v>
+        <v>478304</v>
       </c>
       <c r="R10" t="n">
-        <v>6790967</v>
+        <v>6790950</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,11 +1624,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i en radie av ca 30 meter. Tallar och granar med ålder mer än 150 år</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,10 +1650,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123220064</v>
+        <v>123238030</v>
       </c>
       <c r="B11" t="n">
-        <v>56078</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1669,39 +1666,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478304</v>
+        <v>478302</v>
       </c>
       <c r="R11" t="n">
-        <v>6790950</v>
+        <v>6791004</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1736,6 +1736,11 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Trumning från två håll i pågående avverkningsområde vilket utförs av Mellanskog!</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1757,6 +1762,1005 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>123267228</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Skarpmyrarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>478259</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6791003</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom synfältet, ca 30 meter i radie. Hänger i grenverk på t ex tall av hög ålder, ca 200 år eller mer enligt bild.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>123268324</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Skarpmyrarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>478295</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6790710</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Synliga rester av garnlav i avverkat område. Bilder över det pågående avverkade området. Räknade årsringar och kom till mer än 200 år!</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>123269013</v>
+      </c>
+      <c r="B14" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Skarpmyrarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>478369</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6790685</v>
+      </c>
+      <c r="S14" t="n">
+        <v>50</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Miljöbilder som visar rester av garnlav i avverkningsområdet.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>123267825</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Skarpmyrarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>478316</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6790830</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Troligen hackspår efter tretåig hackspett.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>123269295</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Skarpmyrarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>478427</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6790640</v>
+      </c>
+      <c r="S16" t="n">
+        <v>50</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Miljöbilder med garnlav.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>123265474</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Skarpmyrarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>478414</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6790720</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Troligt använt bo förra säsongen, inringat på bild.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>123268735</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Skarpmyrarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>478301</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6790602</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Troligen hackmärken från tretåig hackspett.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>123267441</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Skarpmyrarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>478340</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6790914</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav synligt i en radie av ca 25 meter. Bilden visar en av många äldre granar med garnlav. Även hackspår syns på stammen.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>123267612</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Skarpmyrarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>478347</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6790843</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Garnlav på tallstam vid skördare!</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48499-2024 artfynd.xlsx
+++ b/artfynd/A 48499-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123222590</v>
+        <v>123222386</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478246</v>
+        <v>478251</v>
       </c>
       <c r="R2" t="n">
-        <v>6790623</v>
+        <v>6790651</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i området. I alla riktningar sp långt man ser.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123225324</v>
+        <v>123220064</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>56078</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478477</v>
+        <v>478304</v>
       </c>
       <c r="R3" t="n">
-        <v>6790674</v>
+        <v>6790950</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -863,11 +863,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Tretå hack mitt i avverkningsområdet där även gallring utförts utan att ha uppmärksammat spåren!</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123220381</v>
+        <v>123219384</v>
       </c>
       <c r="B4" t="n">
         <v>78766</v>
@@ -934,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478362</v>
+        <v>478302</v>
       </c>
       <c r="R4" t="n">
-        <v>6790876</v>
+        <v>6791004</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,6 +965,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123237971</v>
+        <v>123225324</v>
       </c>
       <c r="B5" t="n">
         <v>57478</v>
@@ -1029,32 +1029,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478334</v>
+        <v>478477</v>
       </c>
       <c r="R5" t="n">
-        <v>6790644</v>
+        <v>6790674</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,7 +1081,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Trumning från två håll i pågånde avverkningsområde vilket utförs av Mellanskog!</t>
+          <t>Tretå hack mitt i avverkningsområdet där även gallring utförts utan att ha uppmärksammat spåren!</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123222386</v>
+        <v>123222590</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,34 +1124,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478251</v>
+        <v>478246</v>
       </c>
       <c r="R6" t="n">
-        <v>6790651</v>
+        <v>6790623</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1191,11 +1189,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i området. I alla riktningar sp långt man ser.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1329,7 +1322,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123219384</v>
+        <v>123220031</v>
       </c>
       <c r="B8" t="n">
         <v>78766</v>
@@ -1369,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478302</v>
+        <v>478291</v>
       </c>
       <c r="R8" t="n">
-        <v>6791004</v>
+        <v>6790967</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,7 +1402,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav i en radie av ca 30 meter</t>
+          <t>Rikligt med garnlav i en radie av ca 30 meter. Tallar och granar med ålder mer än 150 år</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1436,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123220031</v>
+        <v>123237971</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1452,37 +1445,49 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478291</v>
+        <v>478334</v>
       </c>
       <c r="R9" t="n">
-        <v>6790967</v>
+        <v>6790644</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1516,7 +1521,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav i en radie av ca 30 meter. Tallar och granar med ålder mer än 150 år</t>
+          <t>Trumning från två håll i pågånde avverkningsområde vilket utförs av Mellanskog!</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1543,10 +1548,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123220064</v>
+        <v>123220381</v>
       </c>
       <c r="B10" t="n">
-        <v>56078</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1559,39 +1564,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478304</v>
+        <v>478362</v>
       </c>
       <c r="R10" t="n">
-        <v>6790950</v>
+        <v>6790876</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1650,7 +1650,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123238030</v>
+        <v>123267825</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1686,11 +1686,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1698,10 +1694,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478302</v>
+        <v>478316</v>
       </c>
       <c r="R11" t="n">
-        <v>6791004</v>
+        <v>6790830</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1738,7 +1734,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Trumning från två håll i pågående avverkningsområde vilket utförs av Mellanskog!</t>
+          <t>Troligen hackspår efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1765,10 +1761,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123267228</v>
+        <v>123238030</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1781,26 +1777,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1808,10 +1809,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478259</v>
+        <v>478302</v>
       </c>
       <c r="R12" t="n">
-        <v>6791003</v>
+        <v>6791004</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1848,7 +1849,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom synfältet, ca 30 meter i radie. Hänger i grenverk på t ex tall av hög ålder, ca 200 år eller mer enligt bild.</t>
+          <t>Trumning från två håll i pågående avverkningsområde vilket utförs av Mellanskog!</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1857,7 +1858,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1876,7 +1876,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123268324</v>
+        <v>123269295</v>
       </c>
       <c r="B13" t="n">
         <v>78766</v>
@@ -1919,13 +1919,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478295</v>
+        <v>478427</v>
       </c>
       <c r="R13" t="n">
-        <v>6790710</v>
+        <v>6790640</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Synliga rester av garnlav i avverkat område. Bilder över det pågående avverkade området. Räknade årsringar och kom till mer än 200 år!</t>
+          <t>Miljöbilder med garnlav.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1987,7 +1987,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123269013</v>
+        <v>123267612</v>
       </c>
       <c r="B14" t="n">
         <v>78766</v>
@@ -2030,13 +2030,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478369</v>
+        <v>478347</v>
       </c>
       <c r="R14" t="n">
-        <v>6790685</v>
+        <v>6790843</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Miljöbilder som visar rester av garnlav i avverkningsområdet.</t>
+          <t>Garnlav på tallstam vid skördare!</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2098,10 +2098,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123267825</v>
+        <v>123268324</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2114,27 +2114,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2142,13 +2141,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478316</v>
+        <v>478295</v>
       </c>
       <c r="R15" t="n">
-        <v>6790830</v>
+        <v>6790710</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2182,7 +2181,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Troligen hackspår efter tretåig hackspett.</t>
+          <t>Synliga rester av garnlav i avverkat område. Bilder över det pågående avverkade området. Räknade årsringar och kom till mer än 200 år!</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2191,6 +2190,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2209,7 +2209,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123269295</v>
+        <v>123269013</v>
       </c>
       <c r="B16" t="n">
         <v>78766</v>
@@ -2252,10 +2252,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478427</v>
+        <v>478369</v>
       </c>
       <c r="R16" t="n">
-        <v>6790640</v>
+        <v>6790685</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Miljöbilder med garnlav.</t>
+          <t>Miljöbilder som visar rester av garnlav i avverkningsområdet.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2320,10 +2320,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123265474</v>
+        <v>123267441</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2336,27 +2336,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2364,13 +2363,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478414</v>
+        <v>478340</v>
       </c>
       <c r="R17" t="n">
-        <v>6790720</v>
+        <v>6790914</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2404,7 +2403,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Troligt använt bo förra säsongen, inringat på bild.</t>
+          <t>Rikligt med garnlav synligt i en radie av ca 25 meter. Bilden visar en av många äldre granar med garnlav. Även hackspår syns på stammen.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2413,6 +2412,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2542,7 +2542,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123267441</v>
+        <v>123267228</v>
       </c>
       <c r="B19" t="n">
         <v>78766</v>
@@ -2585,10 +2585,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478340</v>
+        <v>478259</v>
       </c>
       <c r="R19" t="n">
-        <v>6790914</v>
+        <v>6791003</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2625,7 +2625,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav synligt i en radie av ca 25 meter. Bilden visar en av många äldre granar med garnlav. Även hackspår syns på stammen.</t>
+          <t>Rikligt med garnlav inom synfältet, ca 30 meter i radie. Hänger i grenverk på t ex tall av hög ålder, ca 200 år eller mer enligt bild.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2653,10 +2653,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123267612</v>
+        <v>123265474</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2669,26 +2669,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2696,13 +2697,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478347</v>
+        <v>478414</v>
       </c>
       <c r="R20" t="n">
-        <v>6790843</v>
+        <v>6790720</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2736,7 +2737,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Garnlav på tallstam vid skördare!</t>
+          <t>Troligt använt bo förra säsongen, inringat på bild.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2745,7 +2746,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 48499-2024 artfynd.xlsx
+++ b/artfynd/A 48499-2024 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123220064</v>
+        <v>123237971</v>
       </c>
       <c r="B3" t="n">
-        <v>56078</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,42 +798,49 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478304</v>
+        <v>478334</v>
       </c>
       <c r="R3" t="n">
-        <v>6790950</v>
+        <v>6790644</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,6 +870,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Trumning från två håll i pågånde avverkningsområde vilket utförs av Mellanskog!</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123219384</v>
+        <v>123225119</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,34 +917,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478302</v>
+        <v>478467</v>
       </c>
       <c r="R4" t="n">
-        <v>6791004</v>
+        <v>6790672</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,11 +982,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123225324</v>
+        <v>123220031</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,39 +1024,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478477</v>
+        <v>478291</v>
       </c>
       <c r="R5" t="n">
-        <v>6790674</v>
+        <v>6790967</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1088,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Tretå hack mitt i avverkningsområdet där även gallring utförts utan att ha uppmärksammat spåren!</t>
+          <t>Rikligt med garnlav i en radie av ca 30 meter. Tallar och granar med ålder mer än 150 år</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1215,7 +1222,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123225119</v>
+        <v>123225324</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1260,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478467</v>
+        <v>478477</v>
       </c>
       <c r="R7" t="n">
-        <v>6790672</v>
+        <v>6790674</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,6 +1303,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Tretå hack mitt i avverkningsområdet där även gallring utförts utan att ha uppmärksammat spåren!</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,7 +1334,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123220031</v>
+        <v>123219384</v>
       </c>
       <c r="B8" t="n">
         <v>78766</v>
@@ -1362,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478291</v>
+        <v>478302</v>
       </c>
       <c r="R8" t="n">
-        <v>6790967</v>
+        <v>6791004</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,7 +1414,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav i en radie av ca 30 meter. Tallar och granar med ålder mer än 150 år</t>
+          <t>Rikligt med garnlav i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1429,10 +1441,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123237971</v>
+        <v>123220064</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>56078</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1445,49 +1457,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478334</v>
+        <v>478304</v>
       </c>
       <c r="R9" t="n">
-        <v>6790644</v>
+        <v>6790950</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1517,11 +1522,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Trumning från två håll i pågånde avverkningsområde vilket utförs av Mellanskog!</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1650,7 +1650,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123267825</v>
+        <v>123268735</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1694,13 +1694,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478316</v>
+        <v>478301</v>
       </c>
       <c r="R11" t="n">
-        <v>6790830</v>
+        <v>6790602</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Troligen hackspår efter tretåig hackspett.</t>
+          <t>Troligen hackmärken från tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1761,10 +1761,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123238030</v>
+        <v>123267612</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1777,31 +1777,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1809,10 +1804,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478302</v>
+        <v>478347</v>
       </c>
       <c r="R12" t="n">
-        <v>6791004</v>
+        <v>6790843</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1849,7 +1844,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Trumning från två håll i pågående avverkningsområde vilket utförs av Mellanskog!</t>
+          <t>Garnlav på tallstam vid skördare!</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1858,6 +1853,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1876,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123269295</v>
+        <v>123267825</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1892,26 +1888,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1919,13 +1916,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478427</v>
+        <v>478316</v>
       </c>
       <c r="R13" t="n">
-        <v>6790640</v>
+        <v>6790830</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1959,7 +1956,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Miljöbilder med garnlav.</t>
+          <t>Troligen hackspår efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1968,7 +1965,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1987,7 +1983,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123267612</v>
+        <v>123269013</v>
       </c>
       <c r="B14" t="n">
         <v>78766</v>
@@ -2030,13 +2026,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478347</v>
+        <v>478369</v>
       </c>
       <c r="R14" t="n">
-        <v>6790843</v>
+        <v>6790685</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2070,7 +2066,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Garnlav på tallstam vid skördare!</t>
+          <t>Miljöbilder som visar rester av garnlav i avverkningsområdet.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2098,7 +2094,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123268324</v>
+        <v>123267441</v>
       </c>
       <c r="B15" t="n">
         <v>78766</v>
@@ -2141,13 +2137,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478295</v>
+        <v>478340</v>
       </c>
       <c r="R15" t="n">
-        <v>6790710</v>
+        <v>6790914</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2181,7 +2177,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Synliga rester av garnlav i avverkat område. Bilder över det pågående avverkade området. Räknade årsringar och kom till mer än 200 år!</t>
+          <t>Rikligt med garnlav synligt i en radie av ca 25 meter. Bilden visar en av många äldre granar med garnlav. Även hackspår syns på stammen.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2209,7 +2205,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123269013</v>
+        <v>123269295</v>
       </c>
       <c r="B16" t="n">
         <v>78766</v>
@@ -2252,10 +2248,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478369</v>
+        <v>478427</v>
       </c>
       <c r="R16" t="n">
-        <v>6790685</v>
+        <v>6790640</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2292,7 +2288,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Miljöbilder som visar rester av garnlav i avverkningsområdet.</t>
+          <t>Miljöbilder med garnlav.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2320,7 +2316,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123267441</v>
+        <v>123268324</v>
       </c>
       <c r="B17" t="n">
         <v>78766</v>
@@ -2363,13 +2359,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478340</v>
+        <v>478295</v>
       </c>
       <c r="R17" t="n">
-        <v>6790914</v>
+        <v>6790710</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2403,7 +2399,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav synligt i en radie av ca 25 meter. Bilden visar en av många äldre granar med garnlav. Även hackspår syns på stammen.</t>
+          <t>Synliga rester av garnlav i avverkat område. Bilder över det pågående avverkade området. Räknade årsringar och kom till mer än 200 år!</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2431,10 +2427,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123268735</v>
+        <v>123267228</v>
       </c>
       <c r="B18" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2447,27 +2443,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2475,13 +2470,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478301</v>
+        <v>478259</v>
       </c>
       <c r="R18" t="n">
-        <v>6790602</v>
+        <v>6791003</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2515,7 +2510,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Troligen hackmärken från tretåig hackspett.</t>
+          <t>Rikligt med garnlav inom synfältet, ca 30 meter i radie. Hänger i grenverk på t ex tall av hög ålder, ca 200 år eller mer enligt bild.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2524,6 +2519,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2542,10 +2538,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123267228</v>
+        <v>123238030</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2558,26 +2554,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2585,10 +2586,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478259</v>
+        <v>478302</v>
       </c>
       <c r="R19" t="n">
-        <v>6791003</v>
+        <v>6791004</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2625,7 +2626,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom synfältet, ca 30 meter i radie. Hänger i grenverk på t ex tall av hög ålder, ca 200 år eller mer enligt bild.</t>
+          <t>Trumning från två håll i pågående avverkningsområde vilket utförs av Mellanskog!</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2634,7 +2635,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 48499-2024 artfynd.xlsx
+++ b/artfynd/A 48499-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123222386</v>
+        <v>123237971</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,49 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478251</v>
+        <v>478334</v>
       </c>
       <c r="R2" t="n">
-        <v>6790651</v>
+        <v>6790644</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +767,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav i området. I alla riktningar sp långt man ser.</t>
+          <t>Trumning från två håll i pågånde avverkningsområde vilket utförs av Mellanskog!</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123237971</v>
+        <v>123222386</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,49 +810,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478334</v>
+        <v>478251</v>
       </c>
       <c r="R3" t="n">
-        <v>6790644</v>
+        <v>6790651</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Trumning från två håll i pågånde avverkningsområde vilket utförs av Mellanskog!</t>
+          <t>Rikligt med garnlav i området. I alla riktningar sp långt man ser.</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 48499-2024 artfynd.xlsx
+++ b/artfynd/A 48499-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2762,6 +2762,1081 @@
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>123351363</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57494</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Skarpmyrarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>478378</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6790494</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Fuktig miljö där gallring utförts även där skogen står kvar.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>123351656</v>
+      </c>
+      <c r="B22" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Skarpmyrarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>478475</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6790491</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>123350545</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57494</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Skarpmyrarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>478481</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6790519</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>123353670</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Skarpmyrarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>478339</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6790611</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre hackspår på nedtryckt gran.</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>123353192</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Skarpmyrarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>478402</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6790701</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Bo använt förra säsongen, fågelbo även 5 meter bredvid, enligt sista två bilder. Höjd på bohål ca 3 meter.</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>123348213</v>
+      </c>
+      <c r="B26" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Skarpmyrarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>478276</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6790569</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Garnlav med inslag av skägglav. I kant av avverkning.</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>123347214</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57494</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Skarpmyrarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>478304</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6790693</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>123355658</v>
+      </c>
+      <c r="B28" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Skarpmyrarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>478318</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6790752</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Garnlav återfinns som rester efter avverkning i hela området, mer eller mindre.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>123353321</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Skarpmyrarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>478360</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6790647</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>123352253</v>
+      </c>
+      <c r="B30" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Skarpmyrarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>478503</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6790702</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Nertryckt garnlav återfinns i hela området mer eller mindre.</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 48499-2024 artfynd.xlsx
+++ b/artfynd/A 48499-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123237971</v>
+        <v>123222386</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,49 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478334</v>
+        <v>478251</v>
       </c>
       <c r="R2" t="n">
-        <v>6790644</v>
+        <v>6790651</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -767,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Trumning från två håll i pågånde avverkningsområde vilket utförs av Mellanskog!</t>
+          <t>Rikligt med garnlav i området. I alla riktningar sp långt man ser.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123222386</v>
+        <v>123237971</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,37 +798,49 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478251</v>
+        <v>478334</v>
       </c>
       <c r="R3" t="n">
-        <v>6790651</v>
+        <v>6790644</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav i området. I alla riktningar sp långt man ser.</t>
+          <t>Trumning från två håll i pågånde avverkningsområde vilket utförs av Mellanskog!</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 48499-2024 artfynd.xlsx
+++ b/artfynd/A 48499-2024 artfynd.xlsx
@@ -3304,7 +3304,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123348213</v>
+        <v>123355658</v>
       </c>
       <c r="B26" t="n">
         <v>78766</v>
@@ -3344,10 +3344,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478276</v>
+        <v>478318</v>
       </c>
       <c r="R26" t="n">
-        <v>6790569</v>
+        <v>6790752</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Garnlav med inslag av skägglav. I kant av avverkning.</t>
+          <t>Garnlav återfinns som rester efter avverkning i hela området, mer eller mindre.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3518,7 +3518,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123355658</v>
+        <v>123348213</v>
       </c>
       <c r="B28" t="n">
         <v>78766</v>
@@ -3558,10 +3558,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478318</v>
+        <v>478276</v>
       </c>
       <c r="R28" t="n">
-        <v>6790752</v>
+        <v>6790569</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Garnlav återfinns som rester efter avverkning i hela området, mer eller mindre.</t>
+          <t>Garnlav med inslag av skägglav. I kant av avverkning.</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 48499-2024 artfynd.xlsx
+++ b/artfynd/A 48499-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123222386</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>123237971</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123225119</v>
+        <v>123225324</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478467</v>
+        <v>478477</v>
       </c>
       <c r="R4" t="n">
-        <v>6790672</v>
+        <v>6790674</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,6 +982,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Tretå hack mitt i avverkningsområdet där även gallring utförts utan att ha uppmärksammat spåren!</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123220031</v>
+        <v>123219384</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478291</v>
+        <v>478302</v>
       </c>
       <c r="R5" t="n">
-        <v>6790967</v>
+        <v>6791004</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1093,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav i en radie av ca 30 meter. Tallar och granar med ålder mer än 150 år</t>
+          <t>Rikligt med garnlav i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123222590</v>
+        <v>123220064</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>56081</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,21 +1136,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1160,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478246</v>
+        <v>478304</v>
       </c>
       <c r="R6" t="n">
-        <v>6790623</v>
+        <v>6790950</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,10 +1227,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123225324</v>
+        <v>123222590</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478477</v>
+        <v>478246</v>
       </c>
       <c r="R7" t="n">
-        <v>6790674</v>
+        <v>6790623</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1303,11 +1308,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Tretå hack mitt i avverkningsområdet där även gallring utförts utan att ha uppmärksammat spåren!</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1334,10 +1334,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123219384</v>
+        <v>123225119</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>57481</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1350,34 +1350,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478302</v>
+        <v>478467</v>
       </c>
       <c r="R8" t="n">
-        <v>6791004</v>
+        <v>6790672</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1410,11 +1415,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,10 +1441,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123220064</v>
+        <v>123220381</v>
       </c>
       <c r="B9" t="n">
-        <v>56078</v>
+        <v>78769</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1457,39 +1457,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478304</v>
+        <v>478362</v>
       </c>
       <c r="R9" t="n">
-        <v>6790950</v>
+        <v>6790876</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1548,10 +1543,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123220381</v>
+        <v>123220031</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1588,10 +1583,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478362</v>
+        <v>478291</v>
       </c>
       <c r="R10" t="n">
-        <v>6790876</v>
+        <v>6790967</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1624,6 +1619,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i en radie av ca 30 meter. Tallar och granar med ålder mer än 150 år</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1650,10 +1650,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123268735</v>
+        <v>123267441</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>78769</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1666,27 +1666,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1694,13 +1693,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478301</v>
+        <v>478340</v>
       </c>
       <c r="R11" t="n">
-        <v>6790602</v>
+        <v>6790914</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1734,7 +1733,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Troligen hackmärken från tretåig hackspett.</t>
+          <t>Rikligt med garnlav synligt i en radie av ca 25 meter. Bilden visar en av många äldre granar med garnlav. Även hackspår syns på stammen.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1743,6 +1742,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1761,10 +1761,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123267612</v>
+        <v>123269295</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1804,13 +1804,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478347</v>
+        <v>478427</v>
       </c>
       <c r="R12" t="n">
-        <v>6790843</v>
+        <v>6790640</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Garnlav på tallstam vid skördare!</t>
+          <t>Miljöbilder med garnlav.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123267825</v>
+        <v>123268735</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1916,13 +1916,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478316</v>
+        <v>478301</v>
       </c>
       <c r="R13" t="n">
-        <v>6790830</v>
+        <v>6790602</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Troligen hackspår efter tretåig hackspett.</t>
+          <t>Troligen hackmärken från tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1983,10 +1983,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123269013</v>
+        <v>123238030</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>57481</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1999,26 +1999,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2026,13 +2031,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478369</v>
+        <v>478302</v>
       </c>
       <c r="R14" t="n">
-        <v>6790685</v>
+        <v>6791004</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2066,7 +2071,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Miljöbilder som visar rester av garnlav i avverkningsområdet.</t>
+          <t>Trumning från två håll i pågående avverkningsområde vilket utförs av Mellanskog!</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2075,7 +2080,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2094,10 +2098,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123267441</v>
+        <v>123267825</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>57481</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2110,26 +2114,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2137,10 +2142,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478340</v>
+        <v>478316</v>
       </c>
       <c r="R15" t="n">
-        <v>6790914</v>
+        <v>6790830</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2177,7 +2182,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav synligt i en radie av ca 25 meter. Bilden visar en av många äldre granar med garnlav. Även hackspår syns på stammen.</t>
+          <t>Troligen hackspår efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2186,7 +2191,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2205,10 +2209,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123269295</v>
+        <v>123267228</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2248,13 +2252,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478427</v>
+        <v>478259</v>
       </c>
       <c r="R16" t="n">
-        <v>6790640</v>
+        <v>6791003</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2288,7 +2292,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Miljöbilder med garnlav.</t>
+          <t>Rikligt med garnlav inom synfältet, ca 30 meter i radie. Hänger i grenverk på t ex tall av hög ålder, ca 200 år eller mer enligt bild.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2316,10 +2320,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123268324</v>
+        <v>123265474</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>57481</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2332,26 +2336,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2359,10 +2364,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478295</v>
+        <v>478414</v>
       </c>
       <c r="R17" t="n">
-        <v>6790710</v>
+        <v>6790720</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2399,7 +2404,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Synliga rester av garnlav i avverkat område. Bilder över det pågående avverkade området. Räknade årsringar och kom till mer än 200 år!</t>
+          <t>Troligt använt bo förra säsongen, inringat på bild.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2408,7 +2413,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2427,10 +2431,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123267228</v>
+        <v>123267612</v>
       </c>
       <c r="B18" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2470,10 +2474,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478259</v>
+        <v>478347</v>
       </c>
       <c r="R18" t="n">
-        <v>6791003</v>
+        <v>6790843</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2510,7 +2514,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom synfältet, ca 30 meter i radie. Hänger i grenverk på t ex tall av hög ålder, ca 200 år eller mer enligt bild.</t>
+          <t>Garnlav på tallstam vid skördare!</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2538,10 +2542,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123238030</v>
+        <v>123269013</v>
       </c>
       <c r="B19" t="n">
-        <v>57478</v>
+        <v>78769</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2554,31 +2558,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2586,13 +2585,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478302</v>
+        <v>478369</v>
       </c>
       <c r="R19" t="n">
-        <v>6791004</v>
+        <v>6790685</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2626,7 +2625,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Trumning från två håll i pågående avverkningsområde vilket utförs av Mellanskog!</t>
+          <t>Miljöbilder som visar rester av garnlav i avverkningsområdet.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2635,6 +2634,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2653,10 +2653,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123265474</v>
+        <v>123268324</v>
       </c>
       <c r="B20" t="n">
-        <v>57478</v>
+        <v>78769</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2669,27 +2669,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2697,10 +2696,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478414</v>
+        <v>478295</v>
       </c>
       <c r="R20" t="n">
-        <v>6790720</v>
+        <v>6790710</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2737,7 +2736,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Troligt använt bo förra säsongen, inringat på bild.</t>
+          <t>Synliga rester av garnlav i avverkat område. Bilder över det pågående avverkade området. Räknade årsringar och kom till mer än 200 år!</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2746,6 +2745,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123351363</v>
+        <v>123353321</v>
       </c>
       <c r="B21" t="n">
-        <v>57494</v>
+        <v>57481</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2780,16 +2780,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2809,10 +2809,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478378</v>
+        <v>478360</v>
       </c>
       <c r="R21" t="n">
-        <v>6790494</v>
+        <v>6790647</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2845,11 +2845,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Fuktig miljö där gallring utförts även där skogen står kvar.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2879,7 +2874,7 @@
         <v>123351656</v>
       </c>
       <c r="B22" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2978,10 +2973,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123350545</v>
+        <v>123351363</v>
       </c>
       <c r="B23" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3014,7 +3009,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3023,10 +3018,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478481</v>
+        <v>478378</v>
       </c>
       <c r="R23" t="n">
-        <v>6790519</v>
+        <v>6790494</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3059,6 +3054,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Fuktig miljö där gallring utförts även där skogen står kvar.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3088,7 +3088,7 @@
         <v>123353670</v>
       </c>
       <c r="B24" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3197,10 +3197,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123353192</v>
+        <v>123347214</v>
       </c>
       <c r="B25" t="n">
-        <v>57478</v>
+        <v>57497</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3213,16 +3213,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3231,16 +3231,21 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478402</v>
+        <v>478304</v>
       </c>
       <c r="R25" t="n">
-        <v>6790701</v>
+        <v>6790693</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3273,11 +3278,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Bo använt förra säsongen, fågelbo även 5 meter bredvid, enligt sista två bilder. Höjd på bohål ca 3 meter.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3304,10 +3304,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123355658</v>
+        <v>123348213</v>
       </c>
       <c r="B26" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3344,10 +3344,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478318</v>
+        <v>478276</v>
       </c>
       <c r="R26" t="n">
-        <v>6790752</v>
+        <v>6790569</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Garnlav återfinns som rester efter avverkning i hela området, mer eller mindre.</t>
+          <t>Garnlav med inslag av skägglav. I kant av avverkning.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3411,10 +3411,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123347214</v>
+        <v>123352253</v>
       </c>
       <c r="B27" t="n">
-        <v>57494</v>
+        <v>78769</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3427,39 +3427,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478304</v>
+        <v>478503</v>
       </c>
       <c r="R27" t="n">
-        <v>6790693</v>
+        <v>6790702</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3492,6 +3487,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Nertryckt garnlav återfinns i hela området mer eller mindre.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3518,10 +3518,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123348213</v>
+        <v>123353192</v>
       </c>
       <c r="B28" t="n">
-        <v>78766</v>
+        <v>57481</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3534,21 +3534,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3558,10 +3558,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478276</v>
+        <v>478402</v>
       </c>
       <c r="R28" t="n">
-        <v>6790569</v>
+        <v>6790701</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Garnlav med inslag av skägglav. I kant av avverkning.</t>
+          <t>Bo använt förra säsongen, fågelbo även 5 meter bredvid, enligt sista två bilder. Höjd på bohål ca 3 meter.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3625,10 +3625,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123353321</v>
+        <v>123355658</v>
       </c>
       <c r="B29" t="n">
-        <v>57478</v>
+        <v>78769</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3641,39 +3641,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478360</v>
+        <v>478318</v>
       </c>
       <c r="R29" t="n">
-        <v>6790647</v>
+        <v>6790752</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3706,6 +3701,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Garnlav återfinns som rester efter avverkning i hela området, mer eller mindre.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3732,10 +3732,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123352253</v>
+        <v>123350545</v>
       </c>
       <c r="B30" t="n">
-        <v>78766</v>
+        <v>57497</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3748,34 +3748,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478503</v>
+        <v>478481</v>
       </c>
       <c r="R30" t="n">
-        <v>6790702</v>
+        <v>6790519</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3808,11 +3813,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Nertryckt garnlav återfinns i hela området mer eller mindre.</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 48499-2024 artfynd.xlsx
+++ b/artfynd/A 48499-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123222386</v>
+        <v>123220064</v>
       </c>
       <c r="B2" t="n">
-        <v>78769</v>
+        <v>56081</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478251</v>
+        <v>478304</v>
       </c>
       <c r="R2" t="n">
-        <v>6790651</v>
+        <v>6790950</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +756,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i området. I alla riktningar sp långt man ser.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123237971</v>
+        <v>123225119</v>
       </c>
       <c r="B3" t="n">
         <v>57481</v>
@@ -815,32 +815,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478334</v>
+        <v>478467</v>
       </c>
       <c r="R3" t="n">
-        <v>6790644</v>
+        <v>6790672</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,11 +863,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Trumning från två håll i pågånde avverkningsområde vilket utförs av Mellanskog!</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123225324</v>
+        <v>123220031</v>
       </c>
       <c r="B4" t="n">
-        <v>57481</v>
+        <v>78771</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,39 +905,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478477</v>
+        <v>478291</v>
       </c>
       <c r="R4" t="n">
-        <v>6790674</v>
+        <v>6790967</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Tretå hack mitt i avverkningsområdet där även gallring utförts utan att ha uppmärksammat spåren!</t>
+          <t>Rikligt med garnlav i en radie av ca 30 meter. Tallar och granar med ålder mer än 150 år</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123219384</v>
+        <v>123220381</v>
       </c>
       <c r="B5" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1053,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478302</v>
+        <v>478362</v>
       </c>
       <c r="R5" t="n">
-        <v>6791004</v>
+        <v>6790876</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,11 +1072,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123220064</v>
+        <v>123225324</v>
       </c>
       <c r="B6" t="n">
-        <v>56081</v>
+        <v>57481</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1136,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1165,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478304</v>
+        <v>478477</v>
       </c>
       <c r="R6" t="n">
-        <v>6790950</v>
+        <v>6790674</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,6 +1179,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Tretå hack mitt i avverkningsområdet där även gallring utförts utan att ha uppmärksammat spåren!</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1334,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123225119</v>
+        <v>123219384</v>
       </c>
       <c r="B8" t="n">
-        <v>57481</v>
+        <v>78771</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1350,39 +1333,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478467</v>
+        <v>478302</v>
       </c>
       <c r="R8" t="n">
-        <v>6790672</v>
+        <v>6791004</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,6 +1393,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123220381</v>
+        <v>123222386</v>
       </c>
       <c r="B9" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1481,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478362</v>
+        <v>478251</v>
       </c>
       <c r="R9" t="n">
-        <v>6790876</v>
+        <v>6790651</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1517,6 +1500,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i området. I alla riktningar sp långt man ser.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1543,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123220031</v>
+        <v>123237971</v>
       </c>
       <c r="B10" t="n">
-        <v>78769</v>
+        <v>57481</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1559,37 +1547,49 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478291</v>
+        <v>478334</v>
       </c>
       <c r="R10" t="n">
-        <v>6790967</v>
+        <v>6790644</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav i en radie av ca 30 meter. Tallar och granar med ålder mer än 150 år</t>
+          <t>Trumning från två håll i pågånde avverkningsområde vilket utförs av Mellanskog!</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1650,10 +1650,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123267441</v>
+        <v>123268324</v>
       </c>
       <c r="B11" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1693,13 +1693,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478340</v>
+        <v>478295</v>
       </c>
       <c r="R11" t="n">
-        <v>6790914</v>
+        <v>6790710</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav synligt i en radie av ca 25 meter. Bilden visar en av många äldre granar med garnlav. Även hackspår syns på stammen.</t>
+          <t>Synliga rester av garnlav i avverkat område. Bilder över det pågående avverkade området. Räknade årsringar och kom till mer än 200 år!</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1761,10 +1761,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123269295</v>
+        <v>123267825</v>
       </c>
       <c r="B12" t="n">
-        <v>78769</v>
+        <v>57481</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1777,26 +1777,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1804,13 +1805,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478427</v>
+        <v>478316</v>
       </c>
       <c r="R12" t="n">
-        <v>6790640</v>
+        <v>6790830</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1844,7 +1845,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Miljöbilder med garnlav.</t>
+          <t>Troligen hackspår efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1853,7 +1854,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2098,10 +2098,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123267825</v>
+        <v>123269013</v>
       </c>
       <c r="B15" t="n">
-        <v>57481</v>
+        <v>78771</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2114,27 +2114,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2142,13 +2141,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478316</v>
+        <v>478369</v>
       </c>
       <c r="R15" t="n">
-        <v>6790830</v>
+        <v>6790685</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2182,7 +2181,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Troligen hackspår efter tretåig hackspett.</t>
+          <t>Miljöbilder som visar rester av garnlav i avverkningsområdet.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2191,6 +2190,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2209,10 +2209,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123267228</v>
+        <v>123269295</v>
       </c>
       <c r="B16" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2252,13 +2252,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478259</v>
+        <v>478427</v>
       </c>
       <c r="R16" t="n">
-        <v>6791003</v>
+        <v>6790640</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom synfältet, ca 30 meter i radie. Hänger i grenverk på t ex tall av hög ålder, ca 200 år eller mer enligt bild.</t>
+          <t>Miljöbilder med garnlav.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2320,10 +2320,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123265474</v>
+        <v>123267612</v>
       </c>
       <c r="B17" t="n">
-        <v>57481</v>
+        <v>78771</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2336,27 +2336,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2364,13 +2363,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478414</v>
+        <v>478347</v>
       </c>
       <c r="R17" t="n">
-        <v>6790720</v>
+        <v>6790843</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2404,7 +2403,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Troligt använt bo förra säsongen, inringat på bild.</t>
+          <t>Garnlav på tallstam vid skördare!</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2413,6 +2412,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2431,10 +2431,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123267612</v>
+        <v>123267441</v>
       </c>
       <c r="B18" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478347</v>
+        <v>478340</v>
       </c>
       <c r="R18" t="n">
-        <v>6790843</v>
+        <v>6790914</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Garnlav på tallstam vid skördare!</t>
+          <t>Rikligt med garnlav synligt i en radie av ca 25 meter. Bilden visar en av många äldre granar med garnlav. Även hackspår syns på stammen.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2542,10 +2542,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123269013</v>
+        <v>123265474</v>
       </c>
       <c r="B19" t="n">
-        <v>78769</v>
+        <v>57481</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2558,26 +2558,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2585,13 +2586,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478369</v>
+        <v>478414</v>
       </c>
       <c r="R19" t="n">
-        <v>6790685</v>
+        <v>6790720</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2625,7 +2626,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Miljöbilder som visar rester av garnlav i avverkningsområdet.</t>
+          <t>Troligt använt bo förra säsongen, inringat på bild.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2634,7 +2635,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2653,10 +2653,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123268324</v>
+        <v>123267228</v>
       </c>
       <c r="B20" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2696,13 +2696,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478295</v>
+        <v>478259</v>
       </c>
       <c r="R20" t="n">
-        <v>6790710</v>
+        <v>6791003</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Synliga rester av garnlav i avverkat område. Bilder över det pågående avverkade området. Räknade årsringar och kom till mer än 200 år!</t>
+          <t>Rikligt med garnlav inom synfältet, ca 30 meter i radie. Hänger i grenverk på t ex tall av hög ålder, ca 200 år eller mer enligt bild.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2764,10 +2764,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123353321</v>
+        <v>123352253</v>
       </c>
       <c r="B21" t="n">
-        <v>57481</v>
+        <v>78771</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2780,39 +2780,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478360</v>
+        <v>478503</v>
       </c>
       <c r="R21" t="n">
-        <v>6790647</v>
+        <v>6790702</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2845,6 +2840,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Nertryckt garnlav återfinns i hela området mer eller mindre.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2871,10 +2871,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123351656</v>
+        <v>123353321</v>
       </c>
       <c r="B22" t="n">
-        <v>78769</v>
+        <v>57481</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2887,34 +2887,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478475</v>
+        <v>478360</v>
       </c>
       <c r="R22" t="n">
-        <v>6790491</v>
+        <v>6790647</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3085,10 +3090,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123353670</v>
+        <v>123350545</v>
       </c>
       <c r="B24" t="n">
-        <v>57481</v>
+        <v>57497</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3101,16 +3106,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3121,7 +3126,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3130,10 +3135,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478339</v>
+        <v>478481</v>
       </c>
       <c r="R24" t="n">
-        <v>6790611</v>
+        <v>6790519</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3166,11 +3171,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre hackspår på nedtryckt gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3197,10 +3197,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123347214</v>
+        <v>123351656</v>
       </c>
       <c r="B25" t="n">
-        <v>57497</v>
+        <v>78771</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3213,39 +3213,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478304</v>
+        <v>478475</v>
       </c>
       <c r="R25" t="n">
-        <v>6790693</v>
+        <v>6790491</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3307,7 +3302,7 @@
         <v>123348213</v>
       </c>
       <c r="B26" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3411,10 +3406,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123352253</v>
+        <v>123353670</v>
       </c>
       <c r="B27" t="n">
-        <v>78769</v>
+        <v>57481</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3427,34 +3422,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478503</v>
+        <v>478339</v>
       </c>
       <c r="R27" t="n">
-        <v>6790702</v>
+        <v>6790611</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Nertryckt garnlav återfinns i hela området mer eller mindre.</t>
+          <t>Äldre hackspår på nedtryckt gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3518,10 +3518,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123353192</v>
+        <v>123355658</v>
       </c>
       <c r="B28" t="n">
-        <v>57481</v>
+        <v>78771</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3534,21 +3534,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3558,10 +3558,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478402</v>
+        <v>478318</v>
       </c>
       <c r="R28" t="n">
-        <v>6790701</v>
+        <v>6790752</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Bo använt förra säsongen, fågelbo även 5 meter bredvid, enligt sista två bilder. Höjd på bohål ca 3 meter.</t>
+          <t>Garnlav återfinns som rester efter avverkning i hela området, mer eller mindre.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3625,10 +3625,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123355658</v>
+        <v>123353192</v>
       </c>
       <c r="B29" t="n">
-        <v>78769</v>
+        <v>57481</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3641,21 +3641,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3665,10 +3665,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478318</v>
+        <v>478402</v>
       </c>
       <c r="R29" t="n">
-        <v>6790752</v>
+        <v>6790701</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3705,7 +3705,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Garnlav återfinns som rester efter avverkning i hela området, mer eller mindre.</t>
+          <t>Bo använt förra säsongen, fågelbo även 5 meter bredvid, enligt sista två bilder. Höjd på bohål ca 3 meter.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3732,7 +3732,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123350545</v>
+        <v>123347214</v>
       </c>
       <c r="B30" t="n">
         <v>57497</v>
@@ -3768,7 +3768,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3777,10 +3777,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478481</v>
+        <v>478304</v>
       </c>
       <c r="R30" t="n">
-        <v>6790519</v>
+        <v>6790693</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 48499-2024 artfynd.xlsx
+++ b/artfynd/A 48499-2024 artfynd.xlsx
@@ -3625,10 +3625,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123353192</v>
+        <v>123347214</v>
       </c>
       <c r="B29" t="n">
-        <v>57481</v>
+        <v>57497</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3641,16 +3641,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3659,16 +3659,21 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478402</v>
+        <v>478304</v>
       </c>
       <c r="R29" t="n">
-        <v>6790701</v>
+        <v>6790693</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3701,11 +3706,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Bo använt förra säsongen, fågelbo även 5 meter bredvid, enligt sista två bilder. Höjd på bohål ca 3 meter.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3732,10 +3732,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123347214</v>
+        <v>123353192</v>
       </c>
       <c r="B30" t="n">
-        <v>57497</v>
+        <v>57481</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3748,16 +3748,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3766,21 +3766,16 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478304</v>
+        <v>478402</v>
       </c>
       <c r="R30" t="n">
-        <v>6790693</v>
+        <v>6790701</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3813,6 +3808,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Bo använt förra säsongen, fågelbo även 5 meter bredvid, enligt sista två bilder. Höjd på bohål ca 3 meter.</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 48499-2024 artfynd.xlsx
+++ b/artfynd/A 48499-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123220064</v>
+        <v>123222590</v>
       </c>
       <c r="B2" t="n">
-        <v>56081</v>
+        <v>57481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478304</v>
+        <v>478246</v>
       </c>
       <c r="R2" t="n">
-        <v>6790950</v>
+        <v>6790623</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123225119</v>
+        <v>123237971</v>
       </c>
       <c r="B3" t="n">
         <v>57481</v>
@@ -815,25 +815,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478467</v>
+        <v>478334</v>
       </c>
       <c r="R3" t="n">
-        <v>6790672</v>
+        <v>6790644</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,6 +870,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Trumning från två håll i pågånde avverkningsområde vilket utförs av Mellanskog!</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123220031</v>
+        <v>123220381</v>
       </c>
       <c r="B4" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478291</v>
+        <v>478362</v>
       </c>
       <c r="R4" t="n">
-        <v>6790967</v>
+        <v>6790876</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,11 +977,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i en radie av ca 30 meter. Tallar och granar med ålder mer än 150 år</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123220381</v>
+        <v>123220064</v>
       </c>
       <c r="B5" t="n">
-        <v>78771</v>
+        <v>56081</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,34 +1019,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478362</v>
+        <v>478304</v>
       </c>
       <c r="R5" t="n">
-        <v>6790876</v>
+        <v>6790950</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123225324</v>
+        <v>123222386</v>
       </c>
       <c r="B6" t="n">
-        <v>57481</v>
+        <v>78772</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,39 +1126,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478477</v>
+        <v>478251</v>
       </c>
       <c r="R6" t="n">
-        <v>6790674</v>
+        <v>6790651</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1190,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Tretå hack mitt i avverkningsområdet där även gallring utförts utan att ha uppmärksammat spåren!</t>
+          <t>Rikligt med garnlav i området. I alla riktningar sp långt man ser.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1217,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123222590</v>
+        <v>123219384</v>
       </c>
       <c r="B7" t="n">
-        <v>57481</v>
+        <v>78772</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,39 +1233,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478246</v>
+        <v>478302</v>
       </c>
       <c r="R7" t="n">
-        <v>6790623</v>
+        <v>6791004</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1291,6 +1293,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1324,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123219384</v>
+        <v>123220031</v>
       </c>
       <c r="B8" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,10 +1364,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478302</v>
+        <v>478291</v>
       </c>
       <c r="R8" t="n">
-        <v>6791004</v>
+        <v>6790967</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1404,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav i en radie av ca 30 meter</t>
+          <t>Rikligt med garnlav i en radie av ca 30 meter. Tallar och granar med ålder mer än 150 år</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1431,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123222386</v>
+        <v>123225119</v>
       </c>
       <c r="B9" t="n">
-        <v>78771</v>
+        <v>57481</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1440,34 +1447,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478251</v>
+        <v>478467</v>
       </c>
       <c r="R9" t="n">
-        <v>6790651</v>
+        <v>6790672</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,11 +1512,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i området. I alla riktningar sp långt man ser.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,7 +1538,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123237971</v>
+        <v>123225324</v>
       </c>
       <c r="B10" t="n">
         <v>57481</v>
@@ -1564,32 +1571,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478334</v>
+        <v>478477</v>
       </c>
       <c r="R10" t="n">
-        <v>6790644</v>
+        <v>6790674</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Trumning från två håll i pågånde avverkningsområde vilket utförs av Mellanskog!</t>
+          <t>Tretå hack mitt i avverkningsområdet där även gallring utförts utan att ha uppmärksammat spåren!</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1650,10 +1650,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123268324</v>
+        <v>123267441</v>
       </c>
       <c r="B11" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1693,13 +1693,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478295</v>
+        <v>478340</v>
       </c>
       <c r="R11" t="n">
-        <v>6790710</v>
+        <v>6790914</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Synliga rester av garnlav i avverkat område. Bilder över det pågående avverkade området. Räknade årsringar och kom till mer än 200 år!</t>
+          <t>Rikligt med garnlav synligt i en radie av ca 25 meter. Bilden visar en av många äldre granar med garnlav. Även hackspår syns på stammen.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1872,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123268735</v>
+        <v>123269295</v>
       </c>
       <c r="B13" t="n">
-        <v>57481</v>
+        <v>78772</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1888,27 +1888,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1916,13 +1915,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478301</v>
+        <v>478427</v>
       </c>
       <c r="R13" t="n">
-        <v>6790602</v>
+        <v>6790640</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1956,7 +1955,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Troligen hackmärken från tretåig hackspett.</t>
+          <t>Miljöbilder med garnlav.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1965,6 +1964,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1983,7 +1983,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123238030</v>
+        <v>123268735</v>
       </c>
       <c r="B14" t="n">
         <v>57481</v>
@@ -2019,11 +2019,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2031,13 +2027,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478302</v>
+        <v>478301</v>
       </c>
       <c r="R14" t="n">
-        <v>6791004</v>
+        <v>6790602</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2071,7 +2067,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Trumning från två håll i pågående avverkningsområde vilket utförs av Mellanskog!</t>
+          <t>Troligen hackmärken från tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2101,7 +2097,7 @@
         <v>123269013</v>
       </c>
       <c r="B15" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2209,10 +2205,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123269295</v>
+        <v>123268324</v>
       </c>
       <c r="B16" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2252,13 +2248,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478427</v>
+        <v>478295</v>
       </c>
       <c r="R16" t="n">
-        <v>6790640</v>
+        <v>6790710</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2292,7 +2288,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Miljöbilder med garnlav.</t>
+          <t>Synliga rester av garnlav i avverkat område. Bilder över det pågående avverkade området. Räknade årsringar och kom till mer än 200 år!</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2320,10 +2316,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123267612</v>
+        <v>123267228</v>
       </c>
       <c r="B17" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2363,10 +2359,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478347</v>
+        <v>478259</v>
       </c>
       <c r="R17" t="n">
-        <v>6790843</v>
+        <v>6791003</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2403,7 +2399,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Garnlav på tallstam vid skördare!</t>
+          <t>Rikligt med garnlav inom synfältet, ca 30 meter i radie. Hänger i grenverk på t ex tall av hög ålder, ca 200 år eller mer enligt bild.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2431,10 +2427,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123267441</v>
+        <v>123238030</v>
       </c>
       <c r="B18" t="n">
-        <v>78771</v>
+        <v>57481</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2447,26 +2443,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2474,10 +2475,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478340</v>
+        <v>478302</v>
       </c>
       <c r="R18" t="n">
-        <v>6790914</v>
+        <v>6791004</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2514,7 +2515,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav synligt i en radie av ca 25 meter. Bilden visar en av många äldre granar med garnlav. Även hackspår syns på stammen.</t>
+          <t>Trumning från två håll i pågående avverkningsområde vilket utförs av Mellanskog!</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2523,7 +2524,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2542,10 +2542,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123265474</v>
+        <v>123267612</v>
       </c>
       <c r="B19" t="n">
-        <v>57481</v>
+        <v>78772</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2558,27 +2558,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2586,13 +2585,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478414</v>
+        <v>478347</v>
       </c>
       <c r="R19" t="n">
-        <v>6790720</v>
+        <v>6790843</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2626,7 +2625,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Troligt använt bo förra säsongen, inringat på bild.</t>
+          <t>Garnlav på tallstam vid skördare!</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2635,6 +2634,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2653,10 +2653,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123267228</v>
+        <v>123265474</v>
       </c>
       <c r="B20" t="n">
-        <v>78771</v>
+        <v>57481</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2669,26 +2669,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2696,13 +2697,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478259</v>
+        <v>478414</v>
       </c>
       <c r="R20" t="n">
-        <v>6791003</v>
+        <v>6790720</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2736,7 +2737,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom synfältet, ca 30 meter i radie. Hänger i grenverk på t ex tall av hög ålder, ca 200 år eller mer enligt bild.</t>
+          <t>Troligt använt bo förra säsongen, inringat på bild.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2745,7 +2746,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123352253</v>
+        <v>123347214</v>
       </c>
       <c r="B21" t="n">
-        <v>78771</v>
+        <v>57497</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2780,34 +2780,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478503</v>
+        <v>478304</v>
       </c>
       <c r="R21" t="n">
-        <v>6790702</v>
+        <v>6790693</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2840,11 +2845,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Nertryckt garnlav återfinns i hela området mer eller mindre.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2871,7 +2871,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123353321</v>
+        <v>123353670</v>
       </c>
       <c r="B22" t="n">
         <v>57481</v>
@@ -2916,10 +2916,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478360</v>
+        <v>478339</v>
       </c>
       <c r="R22" t="n">
-        <v>6790647</v>
+        <v>6790611</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2952,6 +2952,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre hackspår på nedtryckt gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2978,10 +2983,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123351363</v>
+        <v>123348213</v>
       </c>
       <c r="B23" t="n">
-        <v>57497</v>
+        <v>78772</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2994,39 +2999,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478378</v>
+        <v>478276</v>
       </c>
       <c r="R23" t="n">
-        <v>6790494</v>
+        <v>6790569</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Fuktig miljö där gallring utförts även där skogen står kvar.</t>
+          <t>Garnlav med inslag av skägglav. I kant av avverkning.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3090,10 +3090,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123350545</v>
+        <v>123353192</v>
       </c>
       <c r="B24" t="n">
-        <v>57497</v>
+        <v>57481</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3106,16 +3106,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3124,21 +3124,16 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478481</v>
+        <v>478402</v>
       </c>
       <c r="R24" t="n">
-        <v>6790519</v>
+        <v>6790701</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3171,6 +3166,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Bo använt förra säsongen, fågelbo även 5 meter bredvid, enligt sista två bilder. Höjd på bohål ca 3 meter.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3197,10 +3197,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123351656</v>
+        <v>123350545</v>
       </c>
       <c r="B25" t="n">
-        <v>78771</v>
+        <v>57497</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3213,34 +3213,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478475</v>
+        <v>478481</v>
       </c>
       <c r="R25" t="n">
-        <v>6790491</v>
+        <v>6790519</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3299,10 +3304,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123348213</v>
+        <v>123351656</v>
       </c>
       <c r="B26" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3339,10 +3344,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478276</v>
+        <v>478475</v>
       </c>
       <c r="R26" t="n">
-        <v>6790569</v>
+        <v>6790491</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3375,11 +3380,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Garnlav med inslag av skägglav. I kant av avverkning.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3406,7 +3406,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123353670</v>
+        <v>123353321</v>
       </c>
       <c r="B27" t="n">
         <v>57481</v>
@@ -3451,10 +3451,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478339</v>
+        <v>478360</v>
       </c>
       <c r="R27" t="n">
-        <v>6790611</v>
+        <v>6790647</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3487,11 +3487,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Äldre hackspår på nedtryckt gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3521,7 +3516,7 @@
         <v>123355658</v>
       </c>
       <c r="B28" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3625,10 +3620,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123347214</v>
+        <v>123352253</v>
       </c>
       <c r="B29" t="n">
-        <v>57497</v>
+        <v>78772</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3641,39 +3636,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478304</v>
+        <v>478503</v>
       </c>
       <c r="R29" t="n">
-        <v>6790693</v>
+        <v>6790702</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3706,6 +3696,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Nertryckt garnlav återfinns i hela området mer eller mindre.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3732,10 +3727,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123353192</v>
+        <v>123351363</v>
       </c>
       <c r="B30" t="n">
-        <v>57481</v>
+        <v>57497</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3748,16 +3743,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3766,16 +3761,21 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478402</v>
+        <v>478378</v>
       </c>
       <c r="R30" t="n">
-        <v>6790701</v>
+        <v>6790494</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3812,7 +3812,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Bo använt förra säsongen, fågelbo även 5 meter bredvid, enligt sista två bilder. Höjd på bohål ca 3 meter.</t>
+          <t>Fuktig miljö där gallring utförts även där skogen står kvar.</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 48499-2024 artfynd.xlsx
+++ b/artfynd/A 48499-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123222386</v>
+        <v>123237971</v>
       </c>
       <c r="B2" t="n">
-        <v>78775</v>
+        <v>57487</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,49 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478251</v>
+        <v>478334</v>
       </c>
       <c r="R2" t="n">
-        <v>6790651</v>
+        <v>6790644</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +767,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav i området. I alla riktningar sp långt man ser.</t>
+          <t>Trumning från två håll i pågånde avverkningsområde vilket utförs av Mellanskog!</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123219384</v>
+        <v>123220031</v>
       </c>
       <c r="B3" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478302</v>
+        <v>478291</v>
       </c>
       <c r="R3" t="n">
-        <v>6791004</v>
+        <v>6790967</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +874,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav i en radie av ca 30 meter</t>
+          <t>Rikligt med garnlav i en radie av ca 30 meter. Tallar och granar med ålder mer än 150 år</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +904,7 @@
         <v>123225119</v>
       </c>
       <c r="B4" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -996,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123225324</v>
+        <v>123220064</v>
       </c>
       <c r="B5" t="n">
-        <v>57481</v>
+        <v>56087</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478477</v>
+        <v>478304</v>
       </c>
       <c r="R5" t="n">
-        <v>6790674</v>
+        <v>6790950</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,11 +1089,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Tretå hack mitt i avverkningsområdet där även gallring utförts utan att ha uppmärksammat spåren!</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123237971</v>
+        <v>123220381</v>
       </c>
       <c r="B6" t="n">
-        <v>57481</v>
+        <v>78781</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1124,49 +1131,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478334</v>
+        <v>478362</v>
       </c>
       <c r="R6" t="n">
-        <v>6790644</v>
+        <v>6790876</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1196,11 +1191,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Trumning från två håll i pågånde avverkningsområde vilket utförs av Mellanskog!</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1227,10 +1217,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123220064</v>
+        <v>123225324</v>
       </c>
       <c r="B7" t="n">
-        <v>56081</v>
+        <v>57487</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1243,21 +1233,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1272,10 +1262,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478304</v>
+        <v>478477</v>
       </c>
       <c r="R7" t="n">
-        <v>6790950</v>
+        <v>6790674</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,6 +1298,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Tretå hack mitt i avverkningsområdet där även gallring utförts utan att ha uppmärksammat spåren!</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1334,10 +1329,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123220381</v>
+        <v>123222386</v>
       </c>
       <c r="B8" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,10 +1369,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478362</v>
+        <v>478251</v>
       </c>
       <c r="R8" t="n">
-        <v>6790876</v>
+        <v>6790651</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1410,6 +1405,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i området. I alla riktningar sp långt man ser.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1436,10 +1436,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123220031</v>
+        <v>123219384</v>
       </c>
       <c r="B9" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1476,10 +1476,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478291</v>
+        <v>478302</v>
       </c>
       <c r="R9" t="n">
-        <v>6790967</v>
+        <v>6791004</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav i en radie av ca 30 meter. Tallar och granar med ålder mer än 150 år</t>
+          <t>Rikligt med garnlav i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,7 +1546,7 @@
         <v>123222590</v>
       </c>
       <c r="B10" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1650,10 +1650,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123269295</v>
+        <v>123269013</v>
       </c>
       <c r="B11" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478427</v>
+        <v>478369</v>
       </c>
       <c r="R11" t="n">
-        <v>6790640</v>
+        <v>6790685</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Miljöbilder med garnlav.</t>
+          <t>Miljöbilder som visar rester av garnlav i avverkningsområdet.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1761,10 +1761,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123267228</v>
+        <v>123268735</v>
       </c>
       <c r="B12" t="n">
-        <v>78775</v>
+        <v>57487</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1777,26 +1777,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1804,13 +1805,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478259</v>
+        <v>478301</v>
       </c>
       <c r="R12" t="n">
-        <v>6791003</v>
+        <v>6790602</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1844,7 +1845,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom synfältet, ca 30 meter i radie. Hänger i grenverk på t ex tall av hög ålder, ca 200 år eller mer enligt bild.</t>
+          <t>Troligen hackmärken från tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1853,7 +1854,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1872,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123268735</v>
+        <v>123267228</v>
       </c>
       <c r="B13" t="n">
-        <v>57481</v>
+        <v>78781</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1888,27 +1888,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1916,13 +1915,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478301</v>
+        <v>478259</v>
       </c>
       <c r="R13" t="n">
-        <v>6790602</v>
+        <v>6791003</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1956,7 +1955,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Troligen hackmärken från tretåig hackspett.</t>
+          <t>Rikligt med garnlav inom synfältet, ca 30 meter i radie. Hänger i grenverk på t ex tall av hög ålder, ca 200 år eller mer enligt bild.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1965,6 +1964,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1983,10 +1983,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123265474</v>
+        <v>123267612</v>
       </c>
       <c r="B14" t="n">
-        <v>57481</v>
+        <v>78781</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1999,27 +1999,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2027,13 +2026,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478414</v>
+        <v>478347</v>
       </c>
       <c r="R14" t="n">
-        <v>6790720</v>
+        <v>6790843</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2067,7 +2066,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Troligt använt bo förra säsongen, inringat på bild.</t>
+          <t>Garnlav på tallstam vid skördare!</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2076,6 +2075,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2094,10 +2094,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123269013</v>
+        <v>123269295</v>
       </c>
       <c r="B15" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2137,10 +2137,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478369</v>
+        <v>478427</v>
       </c>
       <c r="R15" t="n">
-        <v>6790685</v>
+        <v>6790640</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2177,7 +2177,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Miljöbilder som visar rester av garnlav i avverkningsområdet.</t>
+          <t>Miljöbilder med garnlav.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2205,10 +2205,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123267612</v>
+        <v>123268324</v>
       </c>
       <c r="B16" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478347</v>
+        <v>478295</v>
       </c>
       <c r="R16" t="n">
-        <v>6790843</v>
+        <v>6790710</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Garnlav på tallstam vid skördare!</t>
+          <t>Synliga rester av garnlav i avverkat område. Bilder över det pågående avverkade området. Räknade årsringar och kom till mer än 200 år!</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2319,7 +2319,7 @@
         <v>123267825</v>
       </c>
       <c r="B17" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2427,10 +2427,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123238030</v>
+        <v>123267441</v>
       </c>
       <c r="B18" t="n">
-        <v>57481</v>
+        <v>78781</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2443,31 +2443,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2475,10 +2470,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478302</v>
+        <v>478340</v>
       </c>
       <c r="R18" t="n">
-        <v>6791004</v>
+        <v>6790914</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2515,7 +2510,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Trumning från två håll i pågående avverkningsområde vilket utförs av Mellanskog!</t>
+          <t>Rikligt med garnlav synligt i en radie av ca 25 meter. Bilden visar en av många äldre granar med garnlav. Även hackspår syns på stammen.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2524,6 +2519,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2542,10 +2538,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123267441</v>
+        <v>123265474</v>
       </c>
       <c r="B19" t="n">
-        <v>78775</v>
+        <v>57487</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2558,26 +2554,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2585,13 +2582,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478340</v>
+        <v>478414</v>
       </c>
       <c r="R19" t="n">
-        <v>6790914</v>
+        <v>6790720</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2625,7 +2622,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav synligt i en radie av ca 25 meter. Bilden visar en av många äldre granar med garnlav. Även hackspår syns på stammen.</t>
+          <t>Troligt använt bo förra säsongen, inringat på bild.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2634,7 +2631,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2653,10 +2649,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123268324</v>
+        <v>123238030</v>
       </c>
       <c r="B20" t="n">
-        <v>78775</v>
+        <v>57487</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2669,26 +2665,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2696,13 +2697,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478295</v>
+        <v>478302</v>
       </c>
       <c r="R20" t="n">
-        <v>6790710</v>
+        <v>6791004</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2736,7 +2737,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Synliga rester av garnlav i avverkat område. Bilder över det pågående avverkade området. Räknade årsringar och kom till mer än 200 år!</t>
+          <t>Trumning från två håll i pågående avverkningsområde vilket utförs av Mellanskog!</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2745,7 +2746,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2767,7 +2767,7 @@
         <v>123353321</v>
       </c>
       <c r="B21" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2871,10 +2871,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123348213</v>
+        <v>123350545</v>
       </c>
       <c r="B22" t="n">
-        <v>78775</v>
+        <v>57503</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2887,34 +2887,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478276</v>
+        <v>478481</v>
       </c>
       <c r="R22" t="n">
-        <v>6790569</v>
+        <v>6790519</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2947,11 +2952,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Garnlav med inslag av skägglav. I kant av avverkning.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2978,10 +2978,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123352253</v>
+        <v>123353670</v>
       </c>
       <c r="B23" t="n">
-        <v>78775</v>
+        <v>57487</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2994,34 +2994,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478503</v>
+        <v>478339</v>
       </c>
       <c r="R23" t="n">
-        <v>6790702</v>
+        <v>6790611</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3058,7 +3063,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Nertryckt garnlav återfinns i hela området mer eller mindre.</t>
+          <t>Äldre hackspår på nedtryckt gran.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3085,10 +3090,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123350545</v>
+        <v>123347214</v>
       </c>
       <c r="B24" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3121,7 +3126,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3130,10 +3135,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478481</v>
+        <v>478304</v>
       </c>
       <c r="R24" t="n">
-        <v>6790519</v>
+        <v>6790693</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3192,10 +3197,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123353192</v>
+        <v>123355658</v>
       </c>
       <c r="B25" t="n">
-        <v>57481</v>
+        <v>78781</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3208,21 +3213,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3232,10 +3237,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478402</v>
+        <v>478318</v>
       </c>
       <c r="R25" t="n">
-        <v>6790701</v>
+        <v>6790752</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3272,7 +3277,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Bo använt förra säsongen, fågelbo även 5 meter bredvid, enligt sista två bilder. Höjd på bohål ca 3 meter.</t>
+          <t>Garnlav återfinns som rester efter avverkning i hela området, mer eller mindre.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3302,7 +3307,7 @@
         <v>123351363</v>
       </c>
       <c r="B26" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3411,10 +3416,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123353670</v>
+        <v>123348213</v>
       </c>
       <c r="B27" t="n">
-        <v>57481</v>
+        <v>78781</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3427,39 +3432,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478339</v>
+        <v>478276</v>
       </c>
       <c r="R27" t="n">
-        <v>6790611</v>
+        <v>6790569</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3496,7 +3496,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Äldre hackspår på nedtryckt gran.</t>
+          <t>Garnlav med inslag av skägglav. I kant av avverkning.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3523,10 +3523,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123355658</v>
+        <v>123351656</v>
       </c>
       <c r="B28" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3563,10 +3563,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478318</v>
+        <v>478475</v>
       </c>
       <c r="R28" t="n">
-        <v>6790752</v>
+        <v>6790491</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3599,11 +3599,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Garnlav återfinns som rester efter avverkning i hela området, mer eller mindre.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3630,10 +3625,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123351656</v>
+        <v>123353192</v>
       </c>
       <c r="B29" t="n">
-        <v>78775</v>
+        <v>57487</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3646,21 +3641,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3670,10 +3665,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478475</v>
+        <v>478402</v>
       </c>
       <c r="R29" t="n">
-        <v>6790491</v>
+        <v>6790701</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3706,6 +3701,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Bo använt förra säsongen, fågelbo även 5 meter bredvid, enligt sista två bilder. Höjd på bohål ca 3 meter.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3732,10 +3732,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123347214</v>
+        <v>123352253</v>
       </c>
       <c r="B30" t="n">
-        <v>57497</v>
+        <v>78781</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3748,39 +3748,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478304</v>
+        <v>478503</v>
       </c>
       <c r="R30" t="n">
-        <v>6790693</v>
+        <v>6790702</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3813,6 +3808,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Nertryckt garnlav återfinns i hela området mer eller mindre.</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 48499-2024 artfynd.xlsx
+++ b/artfynd/A 48499-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123237971</v>
+        <v>123220031</v>
       </c>
       <c r="B2" t="n">
-        <v>57487</v>
+        <v>78781</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,49 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478334</v>
+        <v>478291</v>
       </c>
       <c r="R2" t="n">
-        <v>6790644</v>
+        <v>6790967</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -767,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Trumning från två håll i pågånde avverkningsområde vilket utförs av Mellanskog!</t>
+          <t>Rikligt med garnlav i en radie av ca 30 meter. Tallar och granar med ålder mer än 150 år</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123220031</v>
+        <v>123225119</v>
       </c>
       <c r="B3" t="n">
-        <v>78781</v>
+        <v>57487</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,34 +798,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478291</v>
+        <v>478467</v>
       </c>
       <c r="R3" t="n">
-        <v>6790967</v>
+        <v>6790672</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,11 +863,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i en radie av ca 30 meter. Tallar och granar med ålder mer än 150 år</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123225119</v>
+        <v>123220064</v>
       </c>
       <c r="B4" t="n">
-        <v>57487</v>
+        <v>56087</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -946,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478467</v>
+        <v>478304</v>
       </c>
       <c r="R4" t="n">
-        <v>6790672</v>
+        <v>6790950</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123220064</v>
+        <v>123220381</v>
       </c>
       <c r="B5" t="n">
-        <v>56087</v>
+        <v>78781</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,39 +1012,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478304</v>
+        <v>478362</v>
       </c>
       <c r="R5" t="n">
-        <v>6790950</v>
+        <v>6790876</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123220381</v>
+        <v>123225324</v>
       </c>
       <c r="B6" t="n">
-        <v>78781</v>
+        <v>57487</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,34 +1114,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478362</v>
+        <v>478477</v>
       </c>
       <c r="R6" t="n">
-        <v>6790876</v>
+        <v>6790674</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1191,6 +1179,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Tretå hack mitt i avverkningsområdet där även gallring utförts utan att ha uppmärksammat spåren!</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1217,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123225324</v>
+        <v>123222386</v>
       </c>
       <c r="B7" t="n">
-        <v>57487</v>
+        <v>78781</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1233,39 +1226,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478477</v>
+        <v>478251</v>
       </c>
       <c r="R7" t="n">
-        <v>6790674</v>
+        <v>6790651</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Tretå hack mitt i avverkningsområdet där även gallring utförts utan att ha uppmärksammat spåren!</t>
+          <t>Rikligt med garnlav i området. I alla riktningar sp långt man ser.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1329,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123222386</v>
+        <v>123219384</v>
       </c>
       <c r="B8" t="n">
         <v>78781</v>
@@ -1369,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478251</v>
+        <v>478302</v>
       </c>
       <c r="R8" t="n">
-        <v>6790651</v>
+        <v>6791004</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,7 +1397,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav i området. I alla riktningar sp långt man ser.</t>
+          <t>Rikligt med garnlav i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1436,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123219384</v>
+        <v>123222590</v>
       </c>
       <c r="B9" t="n">
-        <v>78781</v>
+        <v>57487</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1452,34 +1440,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478302</v>
+        <v>478246</v>
       </c>
       <c r="R9" t="n">
-        <v>6791004</v>
+        <v>6790623</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1512,11 +1505,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1543,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123222590</v>
+        <v>123269013</v>
       </c>
       <c r="B10" t="n">
-        <v>57487</v>
+        <v>78781</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1559,42 +1547,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478246</v>
+        <v>478369</v>
       </c>
       <c r="R10" t="n">
-        <v>6790623</v>
+        <v>6790685</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1626,12 +1612,18 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Miljöbilder som visar rester av garnlav i avverkningsområdet.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1650,10 +1642,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123269013</v>
+        <v>123268735</v>
       </c>
       <c r="B11" t="n">
-        <v>78781</v>
+        <v>57487</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1666,26 +1658,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1693,13 +1686,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478369</v>
+        <v>478301</v>
       </c>
       <c r="R11" t="n">
-        <v>6790685</v>
+        <v>6790602</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1733,7 +1726,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Miljöbilder som visar rester av garnlav i avverkningsområdet.</t>
+          <t>Troligen hackmärken från tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1742,7 +1735,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1761,10 +1753,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123268735</v>
+        <v>123267228</v>
       </c>
       <c r="B12" t="n">
-        <v>57487</v>
+        <v>78781</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1777,27 +1769,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1805,13 +1796,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478301</v>
+        <v>478259</v>
       </c>
       <c r="R12" t="n">
-        <v>6790602</v>
+        <v>6791003</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1845,7 +1836,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Troligen hackmärken från tretåig hackspett.</t>
+          <t>Rikligt med garnlav inom synfältet, ca 30 meter i radie. Hänger i grenverk på t ex tall av hög ålder, ca 200 år eller mer enligt bild.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1854,6 +1845,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1872,7 +1864,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123267228</v>
+        <v>123267612</v>
       </c>
       <c r="B13" t="n">
         <v>78781</v>
@@ -1915,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478259</v>
+        <v>478347</v>
       </c>
       <c r="R13" t="n">
-        <v>6791003</v>
+        <v>6790843</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1955,7 +1947,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom synfältet, ca 30 meter i radie. Hänger i grenverk på t ex tall av hög ålder, ca 200 år eller mer enligt bild.</t>
+          <t>Garnlav på tallstam vid skördare!</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1983,7 +1975,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123267612</v>
+        <v>123269295</v>
       </c>
       <c r="B14" t="n">
         <v>78781</v>
@@ -2026,13 +2018,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478347</v>
+        <v>478427</v>
       </c>
       <c r="R14" t="n">
-        <v>6790843</v>
+        <v>6790640</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2066,7 +2058,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Garnlav på tallstam vid skördare!</t>
+          <t>Miljöbilder med garnlav.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2094,7 +2086,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123269295</v>
+        <v>123268324</v>
       </c>
       <c r="B15" t="n">
         <v>78781</v>
@@ -2137,13 +2129,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478427</v>
+        <v>478295</v>
       </c>
       <c r="R15" t="n">
-        <v>6790640</v>
+        <v>6790710</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2177,7 +2169,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Miljöbilder med garnlav.</t>
+          <t>Synliga rester av garnlav i avverkat område. Bilder över det pågående avverkade området. Räknade årsringar och kom till mer än 200 år!</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2205,10 +2197,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123268324</v>
+        <v>123267825</v>
       </c>
       <c r="B16" t="n">
-        <v>78781</v>
+        <v>57487</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2221,26 +2213,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2248,13 +2241,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478295</v>
+        <v>478316</v>
       </c>
       <c r="R16" t="n">
-        <v>6790710</v>
+        <v>6790830</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2288,7 +2281,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Synliga rester av garnlav i avverkat område. Bilder över det pågående avverkade området. Räknade årsringar och kom till mer än 200 år!</t>
+          <t>Troligen hackspår efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2297,7 +2290,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2316,10 +2308,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123267825</v>
+        <v>123267441</v>
       </c>
       <c r="B17" t="n">
-        <v>57487</v>
+        <v>78781</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2332,27 +2324,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2360,10 +2351,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478316</v>
+        <v>478340</v>
       </c>
       <c r="R17" t="n">
-        <v>6790830</v>
+        <v>6790914</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2400,7 +2391,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Troligen hackspår efter tretåig hackspett.</t>
+          <t>Rikligt med garnlav synligt i en radie av ca 25 meter. Bilden visar en av många äldre granar med garnlav. Även hackspår syns på stammen.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2409,6 +2400,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2427,10 +2419,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123267441</v>
+        <v>123265474</v>
       </c>
       <c r="B18" t="n">
-        <v>78781</v>
+        <v>57487</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2443,26 +2435,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2470,13 +2463,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478340</v>
+        <v>478414</v>
       </c>
       <c r="R18" t="n">
-        <v>6790914</v>
+        <v>6790720</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2510,7 +2503,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav synligt i en radie av ca 25 meter. Bilden visar en av många äldre granar med garnlav. Även hackspår syns på stammen.</t>
+          <t>Troligt använt bo förra säsongen, inringat på bild.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2519,7 +2512,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2538,7 +2530,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123265474</v>
+        <v>123353321</v>
       </c>
       <c r="B19" t="n">
         <v>57487</v>
@@ -2572,23 +2564,24 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478414</v>
+        <v>478360</v>
       </c>
       <c r="R19" t="n">
-        <v>6790720</v>
+        <v>6790647</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2612,17 +2605,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Troligt använt bo förra säsongen, inringat på bild.</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2649,10 +2637,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123238030</v>
+        <v>123350545</v>
       </c>
       <c r="B20" t="n">
-        <v>57487</v>
+        <v>57503</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2665,16 +2653,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2683,24 +2671,21 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478302</v>
+        <v>478481</v>
       </c>
       <c r="R20" t="n">
-        <v>6791004</v>
+        <v>6790519</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2727,17 +2712,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Trumning från två håll i pågående avverkningsområde vilket utförs av Mellanskog!</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2764,7 +2744,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123353321</v>
+        <v>123353670</v>
       </c>
       <c r="B21" t="n">
         <v>57487</v>
@@ -2809,10 +2789,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478360</v>
+        <v>478339</v>
       </c>
       <c r="R21" t="n">
-        <v>6790647</v>
+        <v>6790611</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2845,6 +2825,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre hackspår på nedtryckt gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2871,7 +2856,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123350545</v>
+        <v>123347214</v>
       </c>
       <c r="B22" t="n">
         <v>57503</v>
@@ -2907,7 +2892,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2916,10 +2901,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478481</v>
+        <v>478304</v>
       </c>
       <c r="R22" t="n">
-        <v>6790519</v>
+        <v>6790693</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2978,10 +2963,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123353670</v>
+        <v>123355658</v>
       </c>
       <c r="B23" t="n">
-        <v>57487</v>
+        <v>78781</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2994,39 +2979,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478339</v>
+        <v>478318</v>
       </c>
       <c r="R23" t="n">
-        <v>6790611</v>
+        <v>6790752</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3063,7 +3043,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Äldre hackspår på nedtryckt gran.</t>
+          <t>Garnlav återfinns som rester efter avverkning i hela området, mer eller mindre.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3090,7 +3070,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123347214</v>
+        <v>123351363</v>
       </c>
       <c r="B24" t="n">
         <v>57503</v>
@@ -3135,10 +3115,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478304</v>
+        <v>478378</v>
       </c>
       <c r="R24" t="n">
-        <v>6790693</v>
+        <v>6790494</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3171,6 +3151,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Fuktig miljö där gallring utförts även där skogen står kvar.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3197,7 +3182,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123355658</v>
+        <v>123348213</v>
       </c>
       <c r="B25" t="n">
         <v>78781</v>
@@ -3237,10 +3222,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478318</v>
+        <v>478276</v>
       </c>
       <c r="R25" t="n">
-        <v>6790752</v>
+        <v>6790569</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3277,7 +3262,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Garnlav återfinns som rester efter avverkning i hela området, mer eller mindre.</t>
+          <t>Garnlav med inslag av skägglav. I kant av avverkning.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3304,10 +3289,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123351363</v>
+        <v>123351656</v>
       </c>
       <c r="B26" t="n">
-        <v>57503</v>
+        <v>78781</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3320,39 +3305,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478378</v>
+        <v>478475</v>
       </c>
       <c r="R26" t="n">
-        <v>6790494</v>
+        <v>6790491</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3385,11 +3365,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Fuktig miljö där gallring utförts även där skogen står kvar.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3416,10 +3391,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123348213</v>
+        <v>123353192</v>
       </c>
       <c r="B27" t="n">
-        <v>78781</v>
+        <v>57487</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3432,21 +3407,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3456,10 +3431,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478276</v>
+        <v>478402</v>
       </c>
       <c r="R27" t="n">
-        <v>6790569</v>
+        <v>6790701</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3496,7 +3471,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Garnlav med inslag av skägglav. I kant av avverkning.</t>
+          <t>Bo använt förra säsongen, fågelbo även 5 meter bredvid, enligt sista två bilder. Höjd på bohål ca 3 meter.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3523,7 +3498,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123351656</v>
+        <v>123352253</v>
       </c>
       <c r="B28" t="n">
         <v>78781</v>
@@ -3563,10 +3538,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478475</v>
+        <v>478503</v>
       </c>
       <c r="R28" t="n">
-        <v>6790491</v>
+        <v>6790702</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3599,6 +3574,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Nertryckt garnlav återfinns i hela området mer eller mindre.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3625,7 +3605,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123353192</v>
+        <v>123237971</v>
       </c>
       <c r="B29" t="n">
         <v>57487</v>
@@ -3658,20 +3638,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478402</v>
+        <v>478334</v>
       </c>
       <c r="R29" t="n">
-        <v>6790701</v>
+        <v>6790644</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3695,17 +3687,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Bo använt förra säsongen, fågelbo även 5 meter bredvid, enligt sista två bilder. Höjd på bohål ca 3 meter.</t>
+          <t>Trumning från två håll i pågånde avverkningsområde vilket utförs av Mellanskog!</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3729,113 +3721,6 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>123352253</v>
-      </c>
-      <c r="B30" t="n">
-        <v>78781</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Skarpmyrarna, Dlr</t>
-        </is>
-      </c>
-      <c r="Q30" t="n">
-        <v>478503</v>
-      </c>
-      <c r="R30" t="n">
-        <v>6790702</v>
-      </c>
-      <c r="S30" t="n">
-        <v>10</v>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Orsa</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>Orsa</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Nertryckt garnlav återfinns i hela området mer eller mindre.</t>
-        </is>
-      </c>
-      <c r="AD30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="inlineStr"/>
-      <c r="AW30" t="inlineStr">
-        <is>
-          <t>Håkan Thenander</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>Håkan Thenander</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48499-2024 artfynd.xlsx
+++ b/artfynd/A 48499-2024 artfynd.xlsx
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123220381</v>
+        <v>123225324</v>
       </c>
       <c r="B5" t="n">
-        <v>78781</v>
+        <v>57487</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,34 +1012,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478362</v>
+        <v>478477</v>
       </c>
       <c r="R5" t="n">
-        <v>6790876</v>
+        <v>6790674</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,6 +1077,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Tretå hack mitt i avverkningsområdet där även gallring utförts utan att ha uppmärksammat spåren!</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123225324</v>
+        <v>123220381</v>
       </c>
       <c r="B6" t="n">
-        <v>57487</v>
+        <v>78781</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,39 +1124,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478477</v>
+        <v>478362</v>
       </c>
       <c r="R6" t="n">
-        <v>6790674</v>
+        <v>6790876</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,11 +1184,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Tretå hack mitt i avverkningsområdet där även gallring utförts utan att ha uppmärksammat spåren!</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 48499-2024 artfynd.xlsx
+++ b/artfynd/A 48499-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123220031</v>
+        <v>123225324</v>
       </c>
       <c r="B2" t="n">
-        <v>78781</v>
+        <v>57490</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478291</v>
+        <v>478477</v>
       </c>
       <c r="R2" t="n">
-        <v>6790967</v>
+        <v>6790674</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +760,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav i en radie av ca 30 meter. Tallar och granar med ålder mer än 150 år</t>
+          <t>Tretå hack mitt i avverkningsområdet där även gallring utförts utan att ha uppmärksammat spåren!</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123225119</v>
+        <v>123220031</v>
       </c>
       <c r="B3" t="n">
-        <v>57487</v>
+        <v>78786</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478467</v>
+        <v>478291</v>
       </c>
       <c r="R3" t="n">
-        <v>6790672</v>
+        <v>6790967</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -863,6 +863,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i en radie av ca 30 meter. Tallar och granar med ålder mer än 150 år</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123220064</v>
+        <v>123219384</v>
       </c>
       <c r="B4" t="n">
-        <v>56087</v>
+        <v>78786</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,39 +910,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478304</v>
+        <v>478302</v>
       </c>
       <c r="R4" t="n">
-        <v>6790950</v>
+        <v>6791004</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,6 +970,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123225324</v>
+        <v>123222590</v>
       </c>
       <c r="B5" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478477</v>
+        <v>478246</v>
       </c>
       <c r="R5" t="n">
-        <v>6790674</v>
+        <v>6790623</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,11 +1082,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Tretå hack mitt i avverkningsområdet där även gallring utförts utan att ha uppmärksammat spåren!</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123220381</v>
+        <v>123225119</v>
       </c>
       <c r="B6" t="n">
-        <v>78781</v>
+        <v>57490</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1124,34 +1124,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478362</v>
+        <v>478467</v>
       </c>
       <c r="R6" t="n">
-        <v>6790876</v>
+        <v>6790672</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123222386</v>
+        <v>123220381</v>
       </c>
       <c r="B7" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478251</v>
+        <v>478362</v>
       </c>
       <c r="R7" t="n">
-        <v>6790651</v>
+        <v>6790876</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,11 +1291,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i området. I alla riktningar sp långt man ser.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123219384</v>
+        <v>123222386</v>
       </c>
       <c r="B8" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478302</v>
+        <v>478251</v>
       </c>
       <c r="R8" t="n">
-        <v>6791004</v>
+        <v>6790651</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav i en radie av ca 30 meter</t>
+          <t>Rikligt med garnlav i området. I alla riktningar sp långt man ser.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123222590</v>
+        <v>123220064</v>
       </c>
       <c r="B9" t="n">
-        <v>57487</v>
+        <v>56090</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1440,21 +1440,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478246</v>
+        <v>478304</v>
       </c>
       <c r="R9" t="n">
-        <v>6790623</v>
+        <v>6790950</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123269013</v>
+        <v>123269295</v>
       </c>
       <c r="B10" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1574,10 +1574,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478369</v>
+        <v>478427</v>
       </c>
       <c r="R10" t="n">
-        <v>6790685</v>
+        <v>6790640</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Miljöbilder som visar rester av garnlav i avverkningsområdet.</t>
+          <t>Miljöbilder med garnlav.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1642,10 +1642,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123268735</v>
+        <v>123265474</v>
       </c>
       <c r="B11" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478301</v>
+        <v>478414</v>
       </c>
       <c r="R11" t="n">
-        <v>6790602</v>
+        <v>6790720</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Troligen hackmärken från tretåig hackspett.</t>
+          <t>Troligt använt bo förra säsongen, inringat på bild.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1753,10 +1753,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123267228</v>
+        <v>123268324</v>
       </c>
       <c r="B12" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1796,13 +1796,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478259</v>
+        <v>478295</v>
       </c>
       <c r="R12" t="n">
-        <v>6791003</v>
+        <v>6790710</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom synfältet, ca 30 meter i radie. Hänger i grenverk på t ex tall av hög ålder, ca 200 år eller mer enligt bild.</t>
+          <t>Synliga rester av garnlav i avverkat område. Bilder över det pågående avverkade området. Räknade årsringar och kom till mer än 200 år!</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1864,10 +1864,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123267612</v>
+        <v>123268735</v>
       </c>
       <c r="B13" t="n">
-        <v>78781</v>
+        <v>57490</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1880,26 +1880,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1907,13 +1908,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478347</v>
+        <v>478301</v>
       </c>
       <c r="R13" t="n">
-        <v>6790843</v>
+        <v>6790602</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1947,7 +1948,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Garnlav på tallstam vid skördare!</t>
+          <t>Troligen hackmärken från tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1956,7 +1957,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1975,10 +1975,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123269295</v>
+        <v>123267825</v>
       </c>
       <c r="B14" t="n">
-        <v>78781</v>
+        <v>57490</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1991,26 +1991,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2018,13 +2019,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478427</v>
+        <v>478316</v>
       </c>
       <c r="R14" t="n">
-        <v>6790640</v>
+        <v>6790830</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2058,7 +2059,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Miljöbilder med garnlav.</t>
+          <t>Troligen hackspår efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2067,7 +2068,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2086,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123268324</v>
+        <v>123267612</v>
       </c>
       <c r="B15" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2129,13 +2129,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478295</v>
+        <v>478347</v>
       </c>
       <c r="R15" t="n">
-        <v>6790710</v>
+        <v>6790843</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Synliga rester av garnlav i avverkat område. Bilder över det pågående avverkade området. Räknade årsringar och kom till mer än 200 år!</t>
+          <t>Garnlav på tallstam vid skördare!</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2197,10 +2197,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123267825</v>
+        <v>123269013</v>
       </c>
       <c r="B16" t="n">
-        <v>57487</v>
+        <v>78786</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2213,27 +2213,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2241,13 +2240,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478316</v>
+        <v>478369</v>
       </c>
       <c r="R16" t="n">
-        <v>6790830</v>
+        <v>6790685</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2281,7 +2280,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Troligen hackspår efter tretåig hackspett.</t>
+          <t>Miljöbilder som visar rester av garnlav i avverkningsområdet.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2290,6 +2289,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2308,10 +2308,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123267441</v>
+        <v>123267228</v>
       </c>
       <c r="B17" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478340</v>
+        <v>478259</v>
       </c>
       <c r="R17" t="n">
-        <v>6790914</v>
+        <v>6791003</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav synligt i en radie av ca 25 meter. Bilden visar en av många äldre granar med garnlav. Även hackspår syns på stammen.</t>
+          <t>Rikligt med garnlav inom synfältet, ca 30 meter i radie. Hänger i grenverk på t ex tall av hög ålder, ca 200 år eller mer enligt bild.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2419,10 +2419,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123265474</v>
+        <v>123267441</v>
       </c>
       <c r="B18" t="n">
-        <v>57487</v>
+        <v>78786</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2435,27 +2435,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2463,13 +2462,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478414</v>
+        <v>478340</v>
       </c>
       <c r="R18" t="n">
-        <v>6790720</v>
+        <v>6790914</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2503,7 +2502,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Troligt använt bo förra säsongen, inringat på bild.</t>
+          <t>Rikligt med garnlav synligt i en radie av ca 25 meter. Bilden visar en av många äldre granar med garnlav. Även hackspår syns på stammen.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2512,6 +2511,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2530,10 +2530,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123353321</v>
+        <v>123352253</v>
       </c>
       <c r="B19" t="n">
-        <v>57487</v>
+        <v>78786</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2546,39 +2546,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478360</v>
+        <v>478503</v>
       </c>
       <c r="R19" t="n">
-        <v>6790647</v>
+        <v>6790702</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2611,6 +2606,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Nertryckt garnlav återfinns i hela området mer eller mindre.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2637,10 +2637,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123350545</v>
+        <v>123351656</v>
       </c>
       <c r="B20" t="n">
-        <v>57503</v>
+        <v>78786</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2653,39 +2653,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478481</v>
+        <v>478475</v>
       </c>
       <c r="R20" t="n">
-        <v>6790519</v>
+        <v>6790491</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2747,7 +2742,7 @@
         <v>123353670</v>
       </c>
       <c r="B21" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2859,7 +2854,7 @@
         <v>123347214</v>
       </c>
       <c r="B22" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2963,10 +2958,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123355658</v>
+        <v>123348213</v>
       </c>
       <c r="B23" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3003,10 +2998,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478318</v>
+        <v>478276</v>
       </c>
       <c r="R23" t="n">
-        <v>6790752</v>
+        <v>6790569</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3043,7 +3038,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Garnlav återfinns som rester efter avverkning i hela området, mer eller mindre.</t>
+          <t>Garnlav med inslag av skägglav. I kant av avverkning.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3070,10 +3065,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123351363</v>
+        <v>123355658</v>
       </c>
       <c r="B24" t="n">
-        <v>57503</v>
+        <v>78786</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3086,39 +3081,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478378</v>
+        <v>478318</v>
       </c>
       <c r="R24" t="n">
-        <v>6790494</v>
+        <v>6790752</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3155,7 +3145,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Fuktig miljö där gallring utförts även där skogen står kvar.</t>
+          <t>Garnlav återfinns som rester efter avverkning i hela området, mer eller mindre.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3182,10 +3172,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123348213</v>
+        <v>123350545</v>
       </c>
       <c r="B25" t="n">
-        <v>78781</v>
+        <v>57506</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3198,34 +3188,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478276</v>
+        <v>478481</v>
       </c>
       <c r="R25" t="n">
-        <v>6790569</v>
+        <v>6790519</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3258,11 +3253,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Garnlav med inslag av skägglav. I kant av avverkning.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3289,10 +3279,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123351656</v>
+        <v>123353321</v>
       </c>
       <c r="B26" t="n">
-        <v>78781</v>
+        <v>57490</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3305,34 +3295,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478475</v>
+        <v>478360</v>
       </c>
       <c r="R26" t="n">
-        <v>6790491</v>
+        <v>6790647</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3391,10 +3386,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123353192</v>
+        <v>123351363</v>
       </c>
       <c r="B27" t="n">
-        <v>57487</v>
+        <v>57506</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3407,16 +3402,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3425,16 +3420,21 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478402</v>
+        <v>478378</v>
       </c>
       <c r="R27" t="n">
-        <v>6790701</v>
+        <v>6790494</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Bo använt förra säsongen, fågelbo även 5 meter bredvid, enligt sista två bilder. Höjd på bohål ca 3 meter.</t>
+          <t>Fuktig miljö där gallring utförts även där skogen står kvar.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3498,10 +3498,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123352253</v>
+        <v>123353192</v>
       </c>
       <c r="B28" t="n">
-        <v>78781</v>
+        <v>57490</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3514,21 +3514,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3538,10 +3538,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478503</v>
+        <v>478402</v>
       </c>
       <c r="R28" t="n">
-        <v>6790702</v>
+        <v>6790701</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Nertryckt garnlav återfinns i hela området mer eller mindre.</t>
+          <t>Bo använt förra säsongen, fågelbo även 5 meter bredvid, enligt sista två bilder. Höjd på bohål ca 3 meter.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3608,7 +3608,7 @@
         <v>123237971</v>
       </c>
       <c r="B29" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>

--- a/artfynd/A 48499-2024 artfynd.xlsx
+++ b/artfynd/A 48499-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123225324</v>
+        <v>123220064</v>
       </c>
       <c r="B2" t="n">
-        <v>57490</v>
+        <v>56090</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478477</v>
+        <v>478304</v>
       </c>
       <c r="R2" t="n">
-        <v>6790674</v>
+        <v>6790950</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,11 +756,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Tretå hack mitt i avverkningsområdet där även gallring utförts utan att ha uppmärksammat spåren!</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123220031</v>
+        <v>123220381</v>
       </c>
       <c r="B3" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478291</v>
+        <v>478362</v>
       </c>
       <c r="R3" t="n">
-        <v>6790967</v>
+        <v>6790876</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -863,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i en radie av ca 30 meter. Tallar och granar med ålder mer än 150 år</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,7 +887,7 @@
         <v>123219384</v>
       </c>
       <c r="B4" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1001,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123222590</v>
+        <v>123225324</v>
       </c>
       <c r="B5" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478246</v>
+        <v>478477</v>
       </c>
       <c r="R5" t="n">
-        <v>6790623</v>
+        <v>6790674</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,6 +1072,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Tretå hack mitt i avverkningsområdet där även gallring utförts utan att ha uppmärksammat spåren!</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123225119</v>
+        <v>123222386</v>
       </c>
       <c r="B6" t="n">
-        <v>57490</v>
+        <v>78788</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1124,39 +1119,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478467</v>
+        <v>478251</v>
       </c>
       <c r="R6" t="n">
-        <v>6790672</v>
+        <v>6790651</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,6 +1179,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i området. I alla riktningar sp långt man ser.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123220381</v>
+        <v>123225119</v>
       </c>
       <c r="B7" t="n">
-        <v>78786</v>
+        <v>57491</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,34 +1226,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478362</v>
+        <v>478467</v>
       </c>
       <c r="R7" t="n">
-        <v>6790876</v>
+        <v>6790672</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123222386</v>
+        <v>123220031</v>
       </c>
       <c r="B8" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478251</v>
+        <v>478291</v>
       </c>
       <c r="R8" t="n">
-        <v>6790651</v>
+        <v>6790967</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav i området. I alla riktningar sp långt man ser.</t>
+          <t>Rikligt med garnlav i en radie av ca 30 meter. Tallar och granar med ålder mer än 150 år</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123220064</v>
+        <v>123222590</v>
       </c>
       <c r="B9" t="n">
-        <v>56090</v>
+        <v>57491</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1440,21 +1440,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478304</v>
+        <v>478246</v>
       </c>
       <c r="R9" t="n">
-        <v>6790950</v>
+        <v>6790623</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123269295</v>
+        <v>123269013</v>
       </c>
       <c r="B10" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1574,10 +1574,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478427</v>
+        <v>478369</v>
       </c>
       <c r="R10" t="n">
-        <v>6790640</v>
+        <v>6790685</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Miljöbilder med garnlav.</t>
+          <t>Miljöbilder som visar rester av garnlav i avverkningsområdet.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1642,10 +1642,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123265474</v>
+        <v>123269295</v>
       </c>
       <c r="B11" t="n">
-        <v>57490</v>
+        <v>78788</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1658,27 +1658,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1686,13 +1685,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478414</v>
+        <v>478427</v>
       </c>
       <c r="R11" t="n">
-        <v>6790720</v>
+        <v>6790640</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1726,7 +1725,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Troligt använt bo förra säsongen, inringat på bild.</t>
+          <t>Miljöbilder med garnlav.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,6 +1734,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1753,10 +1753,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123268324</v>
+        <v>123268735</v>
       </c>
       <c r="B12" t="n">
-        <v>78786</v>
+        <v>57491</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1769,26 +1769,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1796,10 +1797,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478295</v>
+        <v>478301</v>
       </c>
       <c r="R12" t="n">
-        <v>6790710</v>
+        <v>6790602</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1836,7 +1837,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Synliga rester av garnlav i avverkat område. Bilder över det pågående avverkade området. Räknade årsringar och kom till mer än 200 år!</t>
+          <t>Troligen hackmärken från tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1845,7 +1846,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1864,10 +1864,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123268735</v>
+        <v>123265474</v>
       </c>
       <c r="B13" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478301</v>
+        <v>478414</v>
       </c>
       <c r="R13" t="n">
-        <v>6790602</v>
+        <v>6790720</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Troligen hackmärken från tretåig hackspett.</t>
+          <t>Troligt använt bo förra säsongen, inringat på bild.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1975,10 +1975,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123267825</v>
+        <v>123267441</v>
       </c>
       <c r="B14" t="n">
-        <v>57490</v>
+        <v>78788</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1991,27 +1991,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2019,10 +2018,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478316</v>
+        <v>478340</v>
       </c>
       <c r="R14" t="n">
-        <v>6790830</v>
+        <v>6790914</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2059,7 +2058,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Troligen hackspår efter tretåig hackspett.</t>
+          <t>Rikligt med garnlav synligt i en radie av ca 25 meter. Bilden visar en av många äldre granar med garnlav. Även hackspår syns på stammen.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2068,6 +2067,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2089,7 +2089,7 @@
         <v>123267612</v>
       </c>
       <c r="B15" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2197,10 +2197,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123269013</v>
+        <v>123268324</v>
       </c>
       <c r="B16" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478369</v>
+        <v>478295</v>
       </c>
       <c r="R16" t="n">
-        <v>6790685</v>
+        <v>6790710</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Miljöbilder som visar rester av garnlav i avverkningsområdet.</t>
+          <t>Synliga rester av garnlav i avverkat område. Bilder över det pågående avverkade området. Räknade årsringar och kom till mer än 200 år!</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2311,7 +2311,7 @@
         <v>123267228</v>
       </c>
       <c r="B17" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2419,10 +2419,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123267441</v>
+        <v>123267825</v>
       </c>
       <c r="B18" t="n">
-        <v>78786</v>
+        <v>57491</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2435,26 +2435,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2462,10 +2463,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478340</v>
+        <v>478316</v>
       </c>
       <c r="R18" t="n">
-        <v>6790914</v>
+        <v>6790830</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2502,7 +2503,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav synligt i en radie av ca 25 meter. Bilden visar en av många äldre granar med garnlav. Även hackspår syns på stammen.</t>
+          <t>Troligen hackspår efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2511,7 +2512,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2530,10 +2530,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123352253</v>
+        <v>123351656</v>
       </c>
       <c r="B19" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2570,10 +2570,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478503</v>
+        <v>478475</v>
       </c>
       <c r="R19" t="n">
-        <v>6790702</v>
+        <v>6790491</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2606,11 +2606,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Nertryckt garnlav återfinns i hela området mer eller mindre.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2637,10 +2632,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123351656</v>
+        <v>123355658</v>
       </c>
       <c r="B20" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2677,10 +2672,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478475</v>
+        <v>478318</v>
       </c>
       <c r="R20" t="n">
-        <v>6790491</v>
+        <v>6790752</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2713,6 +2708,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Garnlav återfinns som rester efter avverkning i hela området, mer eller mindre.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2739,10 +2739,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123353670</v>
+        <v>123353321</v>
       </c>
       <c r="B21" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2784,10 +2784,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478339</v>
+        <v>478360</v>
       </c>
       <c r="R21" t="n">
-        <v>6790611</v>
+        <v>6790647</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2820,11 +2820,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Äldre hackspår på nedtryckt gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2851,10 +2846,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123347214</v>
+        <v>123350545</v>
       </c>
       <c r="B22" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2887,7 +2882,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2896,10 +2891,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478304</v>
+        <v>478481</v>
       </c>
       <c r="R22" t="n">
-        <v>6790693</v>
+        <v>6790519</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2958,10 +2953,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123348213</v>
+        <v>123353192</v>
       </c>
       <c r="B23" t="n">
-        <v>78786</v>
+        <v>57491</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2974,21 +2969,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2998,10 +2993,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478276</v>
+        <v>478402</v>
       </c>
       <c r="R23" t="n">
-        <v>6790569</v>
+        <v>6790701</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3038,7 +3033,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Garnlav med inslag av skägglav. I kant av avverkning.</t>
+          <t>Bo använt förra säsongen, fågelbo även 5 meter bredvid, enligt sista två bilder. Höjd på bohål ca 3 meter.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3065,10 +3060,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123355658</v>
+        <v>123353670</v>
       </c>
       <c r="B24" t="n">
-        <v>78786</v>
+        <v>57491</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3081,34 +3076,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478318</v>
+        <v>478339</v>
       </c>
       <c r="R24" t="n">
-        <v>6790752</v>
+        <v>6790611</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Garnlav återfinns som rester efter avverkning i hela området, mer eller mindre.</t>
+          <t>Äldre hackspår på nedtryckt gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3172,10 +3172,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123350545</v>
+        <v>123352253</v>
       </c>
       <c r="B25" t="n">
-        <v>57506</v>
+        <v>78788</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3188,39 +3188,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478481</v>
+        <v>478503</v>
       </c>
       <c r="R25" t="n">
-        <v>6790519</v>
+        <v>6790702</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3253,6 +3248,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Nertryckt garnlav återfinns i hela området mer eller mindre.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3279,10 +3279,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123353321</v>
+        <v>123351363</v>
       </c>
       <c r="B26" t="n">
-        <v>57490</v>
+        <v>57507</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3295,16 +3295,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3324,10 +3324,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478360</v>
+        <v>478378</v>
       </c>
       <c r="R26" t="n">
-        <v>6790647</v>
+        <v>6790494</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3360,6 +3360,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Fuktig miljö där gallring utförts även där skogen står kvar.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3386,10 +3391,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123351363</v>
+        <v>123348213</v>
       </c>
       <c r="B27" t="n">
-        <v>57506</v>
+        <v>78788</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3402,39 +3407,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478378</v>
+        <v>478276</v>
       </c>
       <c r="R27" t="n">
-        <v>6790494</v>
+        <v>6790569</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Fuktig miljö där gallring utförts även där skogen står kvar.</t>
+          <t>Garnlav med inslag av skägglav. I kant av avverkning.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3498,10 +3498,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123353192</v>
+        <v>123347214</v>
       </c>
       <c r="B28" t="n">
-        <v>57490</v>
+        <v>57507</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3514,16 +3514,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3532,16 +3532,21 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478402</v>
+        <v>478304</v>
       </c>
       <c r="R28" t="n">
-        <v>6790701</v>
+        <v>6790693</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3574,11 +3579,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Bo använt förra säsongen, fågelbo även 5 meter bredvid, enligt sista två bilder. Höjd på bohål ca 3 meter.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3608,7 +3608,7 @@
         <v>123237971</v>
       </c>
       <c r="B29" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>

--- a/artfynd/A 48499-2024 artfynd.xlsx
+++ b/artfynd/A 48499-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123220064</v>
+        <v>123225324</v>
       </c>
       <c r="B2" t="n">
-        <v>56090</v>
+        <v>57491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478304</v>
+        <v>478477</v>
       </c>
       <c r="R2" t="n">
-        <v>6790950</v>
+        <v>6790674</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,6 +756,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Tretå hack mitt i avverkningsområdet där även gallring utförts utan att ha uppmärksammat spåren!</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123220381</v>
+        <v>123225119</v>
       </c>
       <c r="B3" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478362</v>
+        <v>478467</v>
       </c>
       <c r="R3" t="n">
-        <v>6790876</v>
+        <v>6790672</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +894,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123219384</v>
+        <v>123222386</v>
       </c>
       <c r="B4" t="n">
         <v>78788</v>
@@ -924,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478302</v>
+        <v>478251</v>
       </c>
       <c r="R4" t="n">
-        <v>6791004</v>
+        <v>6790651</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +974,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav i en radie av ca 30 meter</t>
+          <t>Rikligt med garnlav i området. I alla riktningar sp långt man ser.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123225324</v>
+        <v>123219384</v>
       </c>
       <c r="B5" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,39 +1017,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478477</v>
+        <v>478302</v>
       </c>
       <c r="R5" t="n">
-        <v>6790674</v>
+        <v>6791004</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1081,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Tretå hack mitt i avverkningsområdet där även gallring utförts utan att ha uppmärksammat spåren!</t>
+          <t>Rikligt med garnlav i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1108,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123222386</v>
+        <v>123220031</v>
       </c>
       <c r="B6" t="n">
         <v>78788</v>
@@ -1143,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478251</v>
+        <v>478291</v>
       </c>
       <c r="R6" t="n">
-        <v>6790651</v>
+        <v>6790967</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1188,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav i området. I alla riktningar sp långt man ser.</t>
+          <t>Rikligt med garnlav i en radie av ca 30 meter. Tallar och granar med ålder mer än 150 år</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123225119</v>
+        <v>123220381</v>
       </c>
       <c r="B7" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,39 +1231,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478467</v>
+        <v>478362</v>
       </c>
       <c r="R7" t="n">
-        <v>6790672</v>
+        <v>6790876</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123220031</v>
+        <v>123222590</v>
       </c>
       <c r="B8" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,34 +1333,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478291</v>
+        <v>478246</v>
       </c>
       <c r="R8" t="n">
-        <v>6790967</v>
+        <v>6790623</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,11 +1398,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i en radie av ca 30 meter. Tallar och granar med ålder mer än 150 år</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123222590</v>
+        <v>123220064</v>
       </c>
       <c r="B9" t="n">
-        <v>57491</v>
+        <v>56090</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1440,21 +1440,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478246</v>
+        <v>478304</v>
       </c>
       <c r="R9" t="n">
-        <v>6790623</v>
+        <v>6790950</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123269013</v>
+        <v>123265474</v>
       </c>
       <c r="B10" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1547,26 +1547,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1574,13 +1575,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478369</v>
+        <v>478414</v>
       </c>
       <c r="R10" t="n">
-        <v>6790685</v>
+        <v>6790720</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1614,7 +1615,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Miljöbilder som visar rester av garnlav i avverkningsområdet.</t>
+          <t>Troligt använt bo förra säsongen, inringat på bild.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1623,7 +1624,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1642,7 +1642,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123269295</v>
+        <v>123267441</v>
       </c>
       <c r="B11" t="n">
         <v>78788</v>
@@ -1685,13 +1685,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478427</v>
+        <v>478340</v>
       </c>
       <c r="R11" t="n">
-        <v>6790640</v>
+        <v>6790914</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Miljöbilder med garnlav.</t>
+          <t>Rikligt med garnlav synligt i en radie av ca 25 meter. Bilden visar en av många äldre granar med garnlav. Även hackspår syns på stammen.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1753,10 +1753,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123268735</v>
+        <v>123269013</v>
       </c>
       <c r="B12" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1769,27 +1769,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1797,13 +1796,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478301</v>
+        <v>478369</v>
       </c>
       <c r="R12" t="n">
-        <v>6790602</v>
+        <v>6790685</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1837,7 +1836,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Troligen hackmärken från tretåig hackspett.</t>
+          <t>Miljöbilder som visar rester av garnlav i avverkningsområdet.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1846,6 +1845,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1864,10 +1864,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123265474</v>
+        <v>123267612</v>
       </c>
       <c r="B13" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1880,27 +1880,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1908,13 +1907,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478414</v>
+        <v>478347</v>
       </c>
       <c r="R13" t="n">
-        <v>6790720</v>
+        <v>6790843</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1948,7 +1947,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Troligt använt bo förra säsongen, inringat på bild.</t>
+          <t>Garnlav på tallstam vid skördare!</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1957,6 +1956,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1975,7 +1975,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123267441</v>
+        <v>123269295</v>
       </c>
       <c r="B14" t="n">
         <v>78788</v>
@@ -2018,13 +2018,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478340</v>
+        <v>478427</v>
       </c>
       <c r="R14" t="n">
-        <v>6790914</v>
+        <v>6790640</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav synligt i en radie av ca 25 meter. Bilden visar en av många äldre granar med garnlav. Även hackspår syns på stammen.</t>
+          <t>Miljöbilder med garnlav.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2086,7 +2086,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123267612</v>
+        <v>123268324</v>
       </c>
       <c r="B15" t="n">
         <v>78788</v>
@@ -2129,13 +2129,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478347</v>
+        <v>478295</v>
       </c>
       <c r="R15" t="n">
-        <v>6790843</v>
+        <v>6790710</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Garnlav på tallstam vid skördare!</t>
+          <t>Synliga rester av garnlav i avverkat område. Bilder över det pågående avverkade området. Räknade årsringar och kom till mer än 200 år!</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2197,7 +2197,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123268324</v>
+        <v>123267228</v>
       </c>
       <c r="B16" t="n">
         <v>78788</v>
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478295</v>
+        <v>478259</v>
       </c>
       <c r="R16" t="n">
-        <v>6790710</v>
+        <v>6791003</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Synliga rester av garnlav i avverkat område. Bilder över det pågående avverkade området. Räknade årsringar och kom till mer än 200 år!</t>
+          <t>Rikligt med garnlav inom synfältet, ca 30 meter i radie. Hänger i grenverk på t ex tall av hög ålder, ca 200 år eller mer enligt bild.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2308,10 +2308,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123267228</v>
+        <v>123268735</v>
       </c>
       <c r="B17" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2324,26 +2324,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2351,13 +2352,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478259</v>
+        <v>478301</v>
       </c>
       <c r="R17" t="n">
-        <v>6791003</v>
+        <v>6790602</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2391,7 +2392,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom synfältet, ca 30 meter i radie. Hänger i grenverk på t ex tall av hög ålder, ca 200 år eller mer enligt bild.</t>
+          <t>Troligen hackmärken från tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2400,7 +2401,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2530,10 +2530,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123351656</v>
+        <v>123353192</v>
       </c>
       <c r="B19" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2546,21 +2546,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2570,10 +2570,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478475</v>
+        <v>478402</v>
       </c>
       <c r="R19" t="n">
-        <v>6790491</v>
+        <v>6790701</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2606,6 +2606,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Bo använt förra säsongen, fågelbo även 5 meter bredvid, enligt sista två bilder. Höjd på bohål ca 3 meter.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2632,7 +2637,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123355658</v>
+        <v>123351656</v>
       </c>
       <c r="B20" t="n">
         <v>78788</v>
@@ -2672,10 +2677,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478318</v>
+        <v>478475</v>
       </c>
       <c r="R20" t="n">
-        <v>6790752</v>
+        <v>6790491</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2708,11 +2713,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Garnlav återfinns som rester efter avverkning i hela området, mer eller mindre.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2739,10 +2739,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123353321</v>
+        <v>123348213</v>
       </c>
       <c r="B21" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2755,39 +2755,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478360</v>
+        <v>478276</v>
       </c>
       <c r="R21" t="n">
-        <v>6790647</v>
+        <v>6790569</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2820,6 +2815,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Garnlav med inslag av skägglav. I kant av avverkning.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2846,10 +2846,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123350545</v>
+        <v>123353670</v>
       </c>
       <c r="B22" t="n">
-        <v>57507</v>
+        <v>57491</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2862,16 +2862,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2882,7 +2882,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478481</v>
+        <v>478339</v>
       </c>
       <c r="R22" t="n">
-        <v>6790519</v>
+        <v>6790611</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2927,6 +2927,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre hackspår på nedtryckt gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2953,10 +2958,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123353192</v>
+        <v>123355658</v>
       </c>
       <c r="B23" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2969,21 +2974,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2993,10 +2998,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478402</v>
+        <v>478318</v>
       </c>
       <c r="R23" t="n">
-        <v>6790701</v>
+        <v>6790752</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3033,7 +3038,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Bo använt förra säsongen, fågelbo även 5 meter bredvid, enligt sista två bilder. Höjd på bohål ca 3 meter.</t>
+          <t>Garnlav återfinns som rester efter avverkning i hela området, mer eller mindre.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3060,7 +3065,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123353670</v>
+        <v>123353321</v>
       </c>
       <c r="B24" t="n">
         <v>57491</v>
@@ -3105,10 +3110,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478339</v>
+        <v>478360</v>
       </c>
       <c r="R24" t="n">
-        <v>6790611</v>
+        <v>6790647</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3141,11 +3146,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre hackspår på nedtryckt gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3172,10 +3172,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123352253</v>
+        <v>123347214</v>
       </c>
       <c r="B25" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3188,34 +3188,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478503</v>
+        <v>478304</v>
       </c>
       <c r="R25" t="n">
-        <v>6790702</v>
+        <v>6790693</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3248,11 +3253,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Nertryckt garnlav återfinns i hela området mer eller mindre.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3279,7 +3279,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123351363</v>
+        <v>123350545</v>
       </c>
       <c r="B26" t="n">
         <v>57507</v>
@@ -3315,7 +3315,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3324,10 +3324,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478378</v>
+        <v>478481</v>
       </c>
       <c r="R26" t="n">
-        <v>6790494</v>
+        <v>6790519</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3360,11 +3360,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Fuktig miljö där gallring utförts även där skogen står kvar.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3391,7 +3386,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123348213</v>
+        <v>123352253</v>
       </c>
       <c r="B27" t="n">
         <v>78788</v>
@@ -3431,10 +3426,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478276</v>
+        <v>478503</v>
       </c>
       <c r="R27" t="n">
-        <v>6790569</v>
+        <v>6790702</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3471,7 +3466,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Garnlav med inslag av skägglav. I kant av avverkning.</t>
+          <t>Nertryckt garnlav återfinns i hela området mer eller mindre.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3498,7 +3493,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123347214</v>
+        <v>123351363</v>
       </c>
       <c r="B28" t="n">
         <v>57507</v>
@@ -3543,10 +3538,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478304</v>
+        <v>478378</v>
       </c>
       <c r="R28" t="n">
-        <v>6790693</v>
+        <v>6790494</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3579,6 +3574,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Fuktig miljö där gallring utförts även där skogen står kvar.</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 48499-2024 artfynd.xlsx
+++ b/artfynd/A 48499-2024 artfynd.xlsx
@@ -3386,10 +3386,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123352253</v>
+        <v>123351363</v>
       </c>
       <c r="B27" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3402,34 +3402,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478503</v>
+        <v>478378</v>
       </c>
       <c r="R27" t="n">
-        <v>6790702</v>
+        <v>6790494</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3466,7 +3471,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Nertryckt garnlav återfinns i hela området mer eller mindre.</t>
+          <t>Fuktig miljö där gallring utförts även där skogen står kvar.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3493,10 +3498,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123351363</v>
+        <v>123352253</v>
       </c>
       <c r="B28" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3509,39 +3514,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478378</v>
+        <v>478503</v>
       </c>
       <c r="R28" t="n">
-        <v>6790494</v>
+        <v>6790702</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Fuktig miljö där gallring utförts även där skogen står kvar.</t>
+          <t>Nertryckt garnlav återfinns i hela området mer eller mindre.</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 48499-2024 artfynd.xlsx
+++ b/artfynd/A 48499-2024 artfynd.xlsx
@@ -1531,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123265474</v>
+        <v>123267825</v>
       </c>
       <c r="B10" t="n">
         <v>57491</v>
@@ -1575,13 +1575,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478414</v>
+        <v>478316</v>
       </c>
       <c r="R10" t="n">
-        <v>6790720</v>
+        <v>6790830</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Troligt använt bo förra säsongen, inringat på bild.</t>
+          <t>Troligen hackspår efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1642,10 +1642,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123267441</v>
+        <v>123268735</v>
       </c>
       <c r="B11" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1658,26 +1658,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1685,13 +1686,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478340</v>
+        <v>478301</v>
       </c>
       <c r="R11" t="n">
-        <v>6790914</v>
+        <v>6790602</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1725,7 +1726,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav synligt i en radie av ca 25 meter. Bilden visar en av många äldre granar med garnlav. Även hackspår syns på stammen.</t>
+          <t>Troligen hackmärken från tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1734,7 +1735,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1753,7 +1753,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123269013</v>
+        <v>123268324</v>
       </c>
       <c r="B12" t="n">
         <v>78788</v>
@@ -1796,13 +1796,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478369</v>
+        <v>478295</v>
       </c>
       <c r="R12" t="n">
-        <v>6790685</v>
+        <v>6790710</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Miljöbilder som visar rester av garnlav i avverkningsområdet.</t>
+          <t>Synliga rester av garnlav i avverkat område. Bilder över det pågående avverkade området. Räknade årsringar och kom till mer än 200 år!</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1975,7 +1975,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123269295</v>
+        <v>123267441</v>
       </c>
       <c r="B14" t="n">
         <v>78788</v>
@@ -2018,13 +2018,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478427</v>
+        <v>478340</v>
       </c>
       <c r="R14" t="n">
-        <v>6790640</v>
+        <v>6790914</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Miljöbilder med garnlav.</t>
+          <t>Rikligt med garnlav synligt i en radie av ca 25 meter. Bilden visar en av många äldre granar med garnlav. Även hackspår syns på stammen.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2086,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123268324</v>
+        <v>123265474</v>
       </c>
       <c r="B15" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2102,26 +2102,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2129,10 +2130,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478295</v>
+        <v>478414</v>
       </c>
       <c r="R15" t="n">
-        <v>6790710</v>
+        <v>6790720</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2169,7 +2170,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Synliga rester av garnlav i avverkat område. Bilder över det pågående avverkade området. Räknade årsringar och kom till mer än 200 år!</t>
+          <t>Troligt använt bo förra säsongen, inringat på bild.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2178,7 +2179,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2197,7 +2197,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123267228</v>
+        <v>123269295</v>
       </c>
       <c r="B16" t="n">
         <v>78788</v>
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478259</v>
+        <v>478427</v>
       </c>
       <c r="R16" t="n">
-        <v>6791003</v>
+        <v>6790640</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom synfältet, ca 30 meter i radie. Hänger i grenverk på t ex tall av hög ålder, ca 200 år eller mer enligt bild.</t>
+          <t>Miljöbilder med garnlav.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2308,10 +2308,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123268735</v>
+        <v>123267228</v>
       </c>
       <c r="B17" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2324,27 +2324,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2352,13 +2351,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478301</v>
+        <v>478259</v>
       </c>
       <c r="R17" t="n">
-        <v>6790602</v>
+        <v>6791003</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2392,7 +2391,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Troligen hackmärken från tretåig hackspett.</t>
+          <t>Rikligt med garnlav inom synfältet, ca 30 meter i radie. Hänger i grenverk på t ex tall av hög ålder, ca 200 år eller mer enligt bild.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2401,6 +2400,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2419,10 +2419,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123267825</v>
+        <v>123269013</v>
       </c>
       <c r="B18" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2435,27 +2435,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2463,13 +2462,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478316</v>
+        <v>478369</v>
       </c>
       <c r="R18" t="n">
-        <v>6790830</v>
+        <v>6790685</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2503,7 +2502,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Troligen hackspår efter tretåig hackspett.</t>
+          <t>Miljöbilder som visar rester av garnlav i avverkningsområdet.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2512,6 +2511,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2530,10 +2530,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123353192</v>
+        <v>123351656</v>
       </c>
       <c r="B19" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2546,21 +2546,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2570,10 +2570,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478402</v>
+        <v>478475</v>
       </c>
       <c r="R19" t="n">
-        <v>6790701</v>
+        <v>6790491</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2606,11 +2606,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Bo använt förra säsongen, fågelbo även 5 meter bredvid, enligt sista två bilder. Höjd på bohål ca 3 meter.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2637,10 +2632,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123351656</v>
+        <v>123351363</v>
       </c>
       <c r="B20" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2653,34 +2648,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478475</v>
+        <v>478378</v>
       </c>
       <c r="R20" t="n">
-        <v>6790491</v>
+        <v>6790494</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2713,6 +2713,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Fuktig miljö där gallring utförts även där skogen står kvar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2739,10 +2744,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123348213</v>
+        <v>123350545</v>
       </c>
       <c r="B21" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2755,34 +2760,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478276</v>
+        <v>478481</v>
       </c>
       <c r="R21" t="n">
-        <v>6790569</v>
+        <v>6790519</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2815,11 +2825,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Garnlav med inslag av skägglav. I kant av avverkning.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2846,7 +2851,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123353670</v>
+        <v>123353192</v>
       </c>
       <c r="B22" t="n">
         <v>57491</v>
@@ -2880,21 +2885,16 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478339</v>
+        <v>478402</v>
       </c>
       <c r="R22" t="n">
-        <v>6790611</v>
+        <v>6790701</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Äldre hackspår på nedtryckt gran.</t>
+          <t>Bo använt förra säsongen, fågelbo även 5 meter bredvid, enligt sista två bilder. Höjd på bohål ca 3 meter.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2958,10 +2958,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123355658</v>
+        <v>123347214</v>
       </c>
       <c r="B23" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2974,34 +2974,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478318</v>
+        <v>478304</v>
       </c>
       <c r="R23" t="n">
-        <v>6790752</v>
+        <v>6790693</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3034,11 +3039,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Garnlav återfinns som rester efter avverkning i hela området, mer eller mindre.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3065,10 +3065,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123353321</v>
+        <v>123355658</v>
       </c>
       <c r="B24" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3081,39 +3081,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478360</v>
+        <v>478318</v>
       </c>
       <c r="R24" t="n">
-        <v>6790647</v>
+        <v>6790752</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3146,6 +3141,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Garnlav återfinns som rester efter avverkning i hela området, mer eller mindre.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3172,10 +3172,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123347214</v>
+        <v>123353321</v>
       </c>
       <c r="B25" t="n">
-        <v>57507</v>
+        <v>57491</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3188,16 +3188,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3217,10 +3217,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478304</v>
+        <v>478360</v>
       </c>
       <c r="R25" t="n">
-        <v>6790693</v>
+        <v>6790647</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3279,10 +3279,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123350545</v>
+        <v>123352253</v>
       </c>
       <c r="B26" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3295,39 +3295,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478481</v>
+        <v>478503</v>
       </c>
       <c r="R26" t="n">
-        <v>6790519</v>
+        <v>6790702</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3360,6 +3355,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Nertryckt garnlav återfinns i hela området mer eller mindre.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3386,10 +3386,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123351363</v>
+        <v>123353670</v>
       </c>
       <c r="B27" t="n">
-        <v>57507</v>
+        <v>57491</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3402,16 +3402,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3431,10 +3431,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478378</v>
+        <v>478339</v>
       </c>
       <c r="R27" t="n">
-        <v>6790494</v>
+        <v>6790611</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Fuktig miljö där gallring utförts även där skogen står kvar.</t>
+          <t>Äldre hackspår på nedtryckt gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3498,7 +3498,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123352253</v>
+        <v>123348213</v>
       </c>
       <c r="B28" t="n">
         <v>78788</v>
@@ -3538,10 +3538,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478503</v>
+        <v>478276</v>
       </c>
       <c r="R28" t="n">
-        <v>6790702</v>
+        <v>6790569</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Nertryckt garnlav återfinns i hela området mer eller mindre.</t>
+          <t>Garnlav med inslag av skägglav. I kant av avverkning.</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 48499-2024 artfynd.xlsx
+++ b/artfynd/A 48499-2024 artfynd.xlsx
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123267825</v>
+        <v>123269013</v>
       </c>
       <c r="B10" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1547,27 +1547,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1575,13 +1574,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478316</v>
+        <v>478369</v>
       </c>
       <c r="R10" t="n">
-        <v>6790830</v>
+        <v>6790685</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1615,7 +1614,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Troligen hackspår efter tretåig hackspett.</t>
+          <t>Miljöbilder som visar rester av garnlav i avverkningsområdet.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1624,6 +1623,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1642,10 +1642,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123268735</v>
+        <v>123267441</v>
       </c>
       <c r="B11" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1658,27 +1658,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1686,13 +1685,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478301</v>
+        <v>478340</v>
       </c>
       <c r="R11" t="n">
-        <v>6790602</v>
+        <v>6790914</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1726,7 +1725,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Troligen hackmärken från tretåig hackspett.</t>
+          <t>Rikligt med garnlav synligt i en radie av ca 25 meter. Bilden visar en av många äldre granar med garnlav. Även hackspår syns på stammen.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,6 +1734,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1753,10 +1753,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123268324</v>
+        <v>123267825</v>
       </c>
       <c r="B12" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1769,26 +1769,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1796,13 +1797,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478295</v>
+        <v>478316</v>
       </c>
       <c r="R12" t="n">
-        <v>6790710</v>
+        <v>6790830</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1836,7 +1837,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Synliga rester av garnlav i avverkat område. Bilder över det pågående avverkade området. Räknade årsringar och kom till mer än 200 år!</t>
+          <t>Troligen hackspår efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1845,7 +1846,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1864,10 +1864,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123267612</v>
+        <v>123265474</v>
       </c>
       <c r="B13" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1880,26 +1880,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1907,13 +1908,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478347</v>
+        <v>478414</v>
       </c>
       <c r="R13" t="n">
-        <v>6790843</v>
+        <v>6790720</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1947,7 +1948,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Garnlav på tallstam vid skördare!</t>
+          <t>Troligt använt bo förra säsongen, inringat på bild.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1956,7 +1957,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1975,10 +1975,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123267441</v>
+        <v>123268735</v>
       </c>
       <c r="B14" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1991,26 +1991,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2018,13 +2019,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478340</v>
+        <v>478301</v>
       </c>
       <c r="R14" t="n">
-        <v>6790914</v>
+        <v>6790602</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2058,7 +2059,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav synligt i en radie av ca 25 meter. Bilden visar en av många äldre granar med garnlav. Även hackspår syns på stammen.</t>
+          <t>Troligen hackmärken från tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2067,7 +2068,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2086,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123265474</v>
+        <v>123267228</v>
       </c>
       <c r="B15" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2102,27 +2102,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2130,13 +2129,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478414</v>
+        <v>478259</v>
       </c>
       <c r="R15" t="n">
-        <v>6790720</v>
+        <v>6791003</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2170,7 +2169,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Troligt använt bo förra säsongen, inringat på bild.</t>
+          <t>Rikligt med garnlav inom synfältet, ca 30 meter i radie. Hänger i grenverk på t ex tall av hög ålder, ca 200 år eller mer enligt bild.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2179,6 +2178,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2197,7 +2197,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123269295</v>
+        <v>123267612</v>
       </c>
       <c r="B16" t="n">
         <v>78788</v>
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478427</v>
+        <v>478347</v>
       </c>
       <c r="R16" t="n">
-        <v>6790640</v>
+        <v>6790843</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Miljöbilder med garnlav.</t>
+          <t>Garnlav på tallstam vid skördare!</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2308,7 +2308,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123267228</v>
+        <v>123268324</v>
       </c>
       <c r="B17" t="n">
         <v>78788</v>
@@ -2351,13 +2351,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478259</v>
+        <v>478295</v>
       </c>
       <c r="R17" t="n">
-        <v>6791003</v>
+        <v>6790710</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom synfältet, ca 30 meter i radie. Hänger i grenverk på t ex tall av hög ålder, ca 200 år eller mer enligt bild.</t>
+          <t>Synliga rester av garnlav i avverkat område. Bilder över det pågående avverkade området. Räknade årsringar och kom till mer än 200 år!</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2419,7 +2419,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123269013</v>
+        <v>123269295</v>
       </c>
       <c r="B18" t="n">
         <v>78788</v>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478369</v>
+        <v>478427</v>
       </c>
       <c r="R18" t="n">
-        <v>6790685</v>
+        <v>6790640</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2502,7 +2502,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Miljöbilder som visar rester av garnlav i avverkningsområdet.</t>
+          <t>Miljöbilder med garnlav.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2530,10 +2530,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123351656</v>
+        <v>123353670</v>
       </c>
       <c r="B19" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2546,34 +2546,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478475</v>
+        <v>478339</v>
       </c>
       <c r="R19" t="n">
-        <v>6790491</v>
+        <v>6790611</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2606,6 +2611,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre hackspår på nedtryckt gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2632,10 +2642,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123351363</v>
+        <v>123355658</v>
       </c>
       <c r="B20" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2648,39 +2658,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478378</v>
+        <v>478318</v>
       </c>
       <c r="R20" t="n">
-        <v>6790494</v>
+        <v>6790752</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2717,7 +2722,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Fuktig miljö där gallring utförts även där skogen står kvar.</t>
+          <t>Garnlav återfinns som rester efter avverkning i hela området, mer eller mindre.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2744,10 +2749,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123350545</v>
+        <v>123351656</v>
       </c>
       <c r="B21" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2760,39 +2765,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478481</v>
+        <v>478475</v>
       </c>
       <c r="R21" t="n">
-        <v>6790519</v>
+        <v>6790491</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2851,7 +2851,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123353192</v>
+        <v>123353321</v>
       </c>
       <c r="B22" t="n">
         <v>57491</v>
@@ -2885,16 +2885,21 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478402</v>
+        <v>478360</v>
       </c>
       <c r="R22" t="n">
-        <v>6790701</v>
+        <v>6790647</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2927,11 +2932,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Bo använt förra säsongen, fågelbo även 5 meter bredvid, enligt sista två bilder. Höjd på bohål ca 3 meter.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2958,10 +2958,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123347214</v>
+        <v>123348213</v>
       </c>
       <c r="B23" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2974,39 +2974,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478304</v>
+        <v>478276</v>
       </c>
       <c r="R23" t="n">
-        <v>6790693</v>
+        <v>6790569</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3039,6 +3034,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Garnlav med inslag av skägglav. I kant av avverkning.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3065,10 +3065,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123355658</v>
+        <v>123353192</v>
       </c>
       <c r="B24" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3081,21 +3081,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3105,10 +3105,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478318</v>
+        <v>478402</v>
       </c>
       <c r="R24" t="n">
-        <v>6790752</v>
+        <v>6790701</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Garnlav återfinns som rester efter avverkning i hela området, mer eller mindre.</t>
+          <t>Bo använt förra säsongen, fågelbo även 5 meter bredvid, enligt sista två bilder. Höjd på bohål ca 3 meter.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3172,10 +3172,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123353321</v>
+        <v>123347214</v>
       </c>
       <c r="B25" t="n">
-        <v>57491</v>
+        <v>57507</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3188,16 +3188,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3217,10 +3217,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478360</v>
+        <v>478304</v>
       </c>
       <c r="R25" t="n">
-        <v>6790647</v>
+        <v>6790693</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3279,10 +3279,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123352253</v>
+        <v>123350545</v>
       </c>
       <c r="B26" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3295,34 +3295,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478503</v>
+        <v>478481</v>
       </c>
       <c r="R26" t="n">
-        <v>6790702</v>
+        <v>6790519</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3355,11 +3360,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Nertryckt garnlav återfinns i hela området mer eller mindre.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3386,10 +3386,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123353670</v>
+        <v>123351363</v>
       </c>
       <c r="B27" t="n">
-        <v>57491</v>
+        <v>57507</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3402,16 +3402,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3431,10 +3431,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478339</v>
+        <v>478378</v>
       </c>
       <c r="R27" t="n">
-        <v>6790611</v>
+        <v>6790494</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Äldre hackspår på nedtryckt gran.</t>
+          <t>Fuktig miljö där gallring utförts även där skogen står kvar.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3498,7 +3498,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123348213</v>
+        <v>123352253</v>
       </c>
       <c r="B28" t="n">
         <v>78788</v>
@@ -3538,10 +3538,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478276</v>
+        <v>478503</v>
       </c>
       <c r="R28" t="n">
-        <v>6790569</v>
+        <v>6790702</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Garnlav med inslag av skägglav. I kant av avverkning.</t>
+          <t>Nertryckt garnlav återfinns i hela området mer eller mindre.</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 48499-2024 artfynd.xlsx
+++ b/artfynd/A 48499-2024 artfynd.xlsx
@@ -2530,7 +2530,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123353670</v>
+        <v>123353321</v>
       </c>
       <c r="B19" t="n">
         <v>57491</v>
@@ -2575,10 +2575,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478339</v>
+        <v>478360</v>
       </c>
       <c r="R19" t="n">
-        <v>6790611</v>
+        <v>6790647</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2611,11 +2611,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre hackspår på nedtryckt gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2642,10 +2637,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123355658</v>
+        <v>123347214</v>
       </c>
       <c r="B20" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2658,34 +2653,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478318</v>
+        <v>478304</v>
       </c>
       <c r="R20" t="n">
-        <v>6790752</v>
+        <v>6790693</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2718,11 +2718,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Garnlav återfinns som rester efter avverkning i hela området, mer eller mindre.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2749,7 +2744,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123351656</v>
+        <v>123355658</v>
       </c>
       <c r="B21" t="n">
         <v>78788</v>
@@ -2789,10 +2784,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478475</v>
+        <v>478318</v>
       </c>
       <c r="R21" t="n">
-        <v>6790491</v>
+        <v>6790752</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2825,6 +2820,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Garnlav återfinns som rester efter avverkning i hela området, mer eller mindre.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2851,10 +2851,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123353321</v>
+        <v>123351363</v>
       </c>
       <c r="B22" t="n">
-        <v>57491</v>
+        <v>57507</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2867,16 +2867,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2896,10 +2896,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478360</v>
+        <v>478378</v>
       </c>
       <c r="R22" t="n">
-        <v>6790647</v>
+        <v>6790494</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2932,6 +2932,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Fuktig miljö där gallring utförts även där skogen står kvar.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3065,10 +3070,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123353192</v>
+        <v>123351656</v>
       </c>
       <c r="B24" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3081,21 +3086,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3105,10 +3110,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478402</v>
+        <v>478475</v>
       </c>
       <c r="R24" t="n">
-        <v>6790701</v>
+        <v>6790491</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3141,11 +3146,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Bo använt förra säsongen, fågelbo även 5 meter bredvid, enligt sista två bilder. Höjd på bohål ca 3 meter.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3172,7 +3172,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123347214</v>
+        <v>123350545</v>
       </c>
       <c r="B25" t="n">
         <v>57507</v>
@@ -3208,7 +3208,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3217,10 +3217,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478304</v>
+        <v>478481</v>
       </c>
       <c r="R25" t="n">
-        <v>6790693</v>
+        <v>6790519</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3279,10 +3279,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123350545</v>
+        <v>123353192</v>
       </c>
       <c r="B26" t="n">
-        <v>57507</v>
+        <v>57491</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3295,16 +3295,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3313,21 +3313,16 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478481</v>
+        <v>478402</v>
       </c>
       <c r="R26" t="n">
-        <v>6790519</v>
+        <v>6790701</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3360,6 +3355,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Bo använt förra säsongen, fågelbo även 5 meter bredvid, enligt sista två bilder. Höjd på bohål ca 3 meter.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3386,10 +3386,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123351363</v>
+        <v>123353670</v>
       </c>
       <c r="B27" t="n">
-        <v>57507</v>
+        <v>57491</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3402,16 +3402,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3431,10 +3431,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478378</v>
+        <v>478339</v>
       </c>
       <c r="R27" t="n">
-        <v>6790494</v>
+        <v>6790611</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Fuktig miljö där gallring utförts även där skogen står kvar.</t>
+          <t>Äldre hackspår på nedtryckt gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 48499-2024 artfynd.xlsx
+++ b/artfynd/A 48499-2024 artfynd.xlsx
@@ -2530,10 +2530,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123353321</v>
+        <v>123347214</v>
       </c>
       <c r="B19" t="n">
-        <v>57491</v>
+        <v>57507</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2546,16 +2546,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2575,10 +2575,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478360</v>
+        <v>478304</v>
       </c>
       <c r="R19" t="n">
-        <v>6790647</v>
+        <v>6790693</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2637,10 +2637,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123347214</v>
+        <v>123353321</v>
       </c>
       <c r="B20" t="n">
-        <v>57507</v>
+        <v>57491</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2653,16 +2653,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2682,10 +2682,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478304</v>
+        <v>478360</v>
       </c>
       <c r="R20" t="n">
-        <v>6790693</v>
+        <v>6790647</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 48499-2024 artfynd.xlsx
+++ b/artfynd/A 48499-2024 artfynd.xlsx
@@ -2530,7 +2530,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123347214</v>
+        <v>123351363</v>
       </c>
       <c r="B19" t="n">
         <v>57507</v>
@@ -2575,10 +2575,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478304</v>
+        <v>478378</v>
       </c>
       <c r="R19" t="n">
-        <v>6790693</v>
+        <v>6790494</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2611,6 +2611,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Fuktig miljö där gallring utförts även där skogen står kvar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2637,10 +2642,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123353321</v>
+        <v>123352253</v>
       </c>
       <c r="B20" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2653,39 +2658,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478360</v>
+        <v>478503</v>
       </c>
       <c r="R20" t="n">
-        <v>6790647</v>
+        <v>6790702</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2718,6 +2718,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Nertryckt garnlav återfinns i hela området mer eller mindre.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2744,10 +2749,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123355658</v>
+        <v>123353670</v>
       </c>
       <c r="B21" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2760,34 +2765,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478318</v>
+        <v>478339</v>
       </c>
       <c r="R21" t="n">
-        <v>6790752</v>
+        <v>6790611</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2824,7 +2834,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Garnlav återfinns som rester efter avverkning i hela området, mer eller mindre.</t>
+          <t>Äldre hackspår på nedtryckt gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2851,10 +2861,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123351363</v>
+        <v>123353192</v>
       </c>
       <c r="B22" t="n">
-        <v>57507</v>
+        <v>57491</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2867,16 +2877,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2885,21 +2895,16 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478378</v>
+        <v>478402</v>
       </c>
       <c r="R22" t="n">
-        <v>6790494</v>
+        <v>6790701</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2936,7 +2941,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Fuktig miljö där gallring utförts även där skogen står kvar.</t>
+          <t>Bo använt förra säsongen, fågelbo även 5 meter bredvid, enligt sista två bilder. Höjd på bohål ca 3 meter.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3172,7 +3177,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123350545</v>
+        <v>123347214</v>
       </c>
       <c r="B25" t="n">
         <v>57507</v>
@@ -3208,7 +3213,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3217,10 +3222,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478481</v>
+        <v>478304</v>
       </c>
       <c r="R25" t="n">
-        <v>6790519</v>
+        <v>6790693</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3279,10 +3284,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123353192</v>
+        <v>123355658</v>
       </c>
       <c r="B26" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3295,21 +3300,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3319,10 +3324,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478402</v>
+        <v>478318</v>
       </c>
       <c r="R26" t="n">
-        <v>6790701</v>
+        <v>6790752</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3359,7 +3364,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Bo använt förra säsongen, fågelbo även 5 meter bredvid, enligt sista två bilder. Höjd på bohål ca 3 meter.</t>
+          <t>Garnlav återfinns som rester efter avverkning i hela området, mer eller mindre.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3386,7 +3391,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123353670</v>
+        <v>123353321</v>
       </c>
       <c r="B27" t="n">
         <v>57491</v>
@@ -3431,10 +3436,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478339</v>
+        <v>478360</v>
       </c>
       <c r="R27" t="n">
-        <v>6790611</v>
+        <v>6790647</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3467,11 +3472,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Äldre hackspår på nedtryckt gran.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3498,10 +3498,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123352253</v>
+        <v>123350545</v>
       </c>
       <c r="B28" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3514,34 +3514,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478503</v>
+        <v>478481</v>
       </c>
       <c r="R28" t="n">
-        <v>6790702</v>
+        <v>6790519</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3574,11 +3579,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Nertryckt garnlav återfinns i hela området mer eller mindre.</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 48499-2024 artfynd.xlsx
+++ b/artfynd/A 48499-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123225324</v>
+        <v>123219384</v>
       </c>
       <c r="B2" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478477</v>
+        <v>478302</v>
       </c>
       <c r="R2" t="n">
-        <v>6790674</v>
+        <v>6791004</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Tretå hack mitt i avverkningsområdet där även gallring utförts utan att ha uppmärksammat spåren!</t>
+          <t>Rikligt med garnlav i en radie av ca 30 meter</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,55 +777,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123225119</v>
+        <v>123220031</v>
       </c>
       <c r="B3" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478467</v>
+        <v>478291</v>
       </c>
       <c r="R3" t="n">
-        <v>6790672</v>
+        <v>6790967</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,6 +848,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i en radie av ca 30 meter. Tallar och granar med ålder mer än 150 år</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,19 +879,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123222386</v>
+        <v>123220381</v>
       </c>
       <c r="B4" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -934,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478251</v>
+        <v>478362</v>
       </c>
       <c r="R4" t="n">
-        <v>6790651</v>
+        <v>6790876</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,11 +950,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i området. I alla riktningar sp långt man ser.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,19 +976,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123219384</v>
+        <v>123222386</v>
       </c>
       <c r="B5" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1041,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478302</v>
+        <v>478251</v>
       </c>
       <c r="R5" t="n">
-        <v>6791004</v>
+        <v>6790651</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1051,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav i en radie av ca 30 meter</t>
+          <t>Rikligt med garnlav i området. I alla riktningar sp långt man ser.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,19 +1078,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123220031</v>
+        <v>123267228</v>
       </c>
       <c r="B6" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1142,16 +1107,19 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478291</v>
+        <v>478259</v>
       </c>
       <c r="R6" t="n">
-        <v>6790967</v>
+        <v>6791003</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,7 +1156,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav i en radie av ca 30 meter. Tallar och granar med ålder mer än 150 år</t>
+          <t>Rikligt med garnlav inom synfältet, ca 30 meter i radie. Hänger i grenverk på t ex tall av hög ålder, ca 200 år eller mer enligt bild.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1197,6 +1165,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1215,19 +1184,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123220381</v>
+        <v>123267441</v>
       </c>
       <c r="B7" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1249,16 +1213,19 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478362</v>
+        <v>478340</v>
       </c>
       <c r="R7" t="n">
-        <v>6790876</v>
+        <v>6790914</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1293,12 +1260,18 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav synligt i en radie av ca 25 meter. Bilden visar en av många äldre granar med garnlav. Även hackspår syns på stammen.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1317,55 +1290,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123222590</v>
+        <v>123267612</v>
       </c>
       <c r="B8" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478246</v>
+        <v>478347</v>
       </c>
       <c r="R8" t="n">
-        <v>6790623</v>
+        <v>6790843</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1400,12 +1366,18 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Garnlav på tallstam vid skördare!</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1424,58 +1396,51 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123220064</v>
+        <v>123268324</v>
       </c>
       <c r="B9" t="n">
-        <v>56090</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478304</v>
+        <v>478295</v>
       </c>
       <c r="R9" t="n">
-        <v>6790950</v>
+        <v>6790710</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1507,12 +1472,18 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Synliga rester av garnlav i avverkat område. Bilder över det pågående avverkade området. Räknade årsringar och kom till mer än 200 år!</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1534,16 +1505,11 @@
         <v>123269013</v>
       </c>
       <c r="B10" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1642,19 +1608,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123267441</v>
+        <v>123269295</v>
       </c>
       <c r="B11" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1685,13 +1646,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478340</v>
+        <v>478427</v>
       </c>
       <c r="R11" t="n">
-        <v>6790914</v>
+        <v>6790640</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1725,7 +1686,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav synligt i en radie av ca 25 meter. Bilden visar en av många äldre granar med garnlav. Även hackspår syns på stammen.</t>
+          <t>Miljöbilder med garnlav.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1753,54 +1714,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123267825</v>
+        <v>123348213</v>
       </c>
       <c r="B12" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478316</v>
+        <v>478276</v>
       </c>
       <c r="R12" t="n">
-        <v>6790830</v>
+        <v>6790569</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1827,17 +1779,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Troligen hackspår efter tretåig hackspett.</t>
+          <t>Garnlav med inslag av skägglav. I kant av avverkning.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1864,57 +1816,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123265474</v>
+        <v>123351656</v>
       </c>
       <c r="B13" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478414</v>
+        <v>478475</v>
       </c>
       <c r="R13" t="n">
-        <v>6790720</v>
+        <v>6790491</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1938,17 +1881,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Troligt använt bo förra säsongen, inringat på bild.</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1975,57 +1913,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123268735</v>
+        <v>123352253</v>
       </c>
       <c r="B14" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478301</v>
+        <v>478503</v>
       </c>
       <c r="R14" t="n">
-        <v>6790602</v>
+        <v>6790702</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2049,17 +1978,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Troligen hackmärken från tretåig hackspett.</t>
+          <t>Nertryckt garnlav återfinns i hela området mer eller mindre.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2086,19 +2015,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123267228</v>
+        <v>123355658</v>
       </c>
       <c r="B15" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2120,19 +2044,16 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478259</v>
+        <v>478318</v>
       </c>
       <c r="R15" t="n">
-        <v>6791003</v>
+        <v>6790752</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,17 +2080,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom synfältet, ca 30 meter i radie. Hänger i grenverk på t ex tall av hög ålder, ca 200 år eller mer enligt bild.</t>
+          <t>Garnlav återfinns som rester efter avverkning i hela området, mer eller mindre.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2178,7 +2099,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2197,19 +2117,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123267612</v>
+        <v>123356603</v>
       </c>
       <c r="B16" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2231,19 +2146,16 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478347</v>
+        <v>478571</v>
       </c>
       <c r="R16" t="n">
-        <v>6790843</v>
+        <v>6790821</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2270,17 +2182,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Garnlav på tallstam vid skördare!</t>
+          <t>Rikligt med garnlav.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2289,7 +2201,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2308,56 +2219,53 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123268324</v>
+        <v>123347214</v>
       </c>
       <c r="B17" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478295</v>
+        <v>478304</v>
       </c>
       <c r="R17" t="n">
-        <v>6790710</v>
+        <v>6790693</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2381,17 +2289,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Synliga rester av garnlav i avverkat område. Bilder över det pågående avverkade området. Räknade årsringar och kom till mer än 200 år!</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2400,7 +2303,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2419,56 +2321,53 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123269295</v>
+        <v>123350545</v>
       </c>
       <c r="B18" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478427</v>
+        <v>478481</v>
       </c>
       <c r="R18" t="n">
-        <v>6790640</v>
+        <v>6790519</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2492,17 +2391,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Miljöbilder med garnlav.</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2511,7 +2405,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2530,19 +2423,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123347214</v>
+        <v>123351363</v>
       </c>
       <c r="B19" t="n">
-        <v>57507</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2575,10 +2463,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478304</v>
+        <v>478378</v>
       </c>
       <c r="R19" t="n">
-        <v>6790693</v>
+        <v>6790494</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2611,6 +2499,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Fuktig miljö där gallring utförts även där skogen står kvar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2637,50 +2530,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123352253</v>
+        <v>123352363</v>
       </c>
       <c r="B20" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478503</v>
+        <v>478515</v>
       </c>
       <c r="R20" t="n">
-        <v>6790702</v>
+        <v>6790699</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2713,11 +2606,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Nertryckt garnlav återfinns i hela området mer eller mindre.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2744,15 +2632,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123348213</v>
+        <v>123222590</v>
       </c>
       <c r="B21" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2760,34 +2643,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478276</v>
+        <v>478246</v>
       </c>
       <c r="R21" t="n">
-        <v>6790569</v>
+        <v>6790623</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2814,17 +2702,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Garnlav med inslag av skägglav. I kant av avverkning.</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2851,15 +2734,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123353670</v>
+        <v>123225119</v>
       </c>
       <c r="B22" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2887,7 +2765,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2896,10 +2774,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478339</v>
+        <v>478467</v>
       </c>
       <c r="R22" t="n">
-        <v>6790611</v>
+        <v>6790672</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2926,17 +2804,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre hackspår på nedtryckt gran.</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2963,15 +2836,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123351363</v>
+        <v>123225324</v>
       </c>
       <c r="B23" t="n">
-        <v>57507</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2979,16 +2847,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2999,7 +2867,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3008,10 +2876,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478378</v>
+        <v>478477</v>
       </c>
       <c r="R23" t="n">
-        <v>6790494</v>
+        <v>6790674</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3038,17 +2906,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Fuktig miljö där gallring utförts även där skogen står kvar.</t>
+          <t>Tretå hack mitt i avverkningsområdet där även gallring utförts utan att ha uppmärksammat spåren!</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3075,15 +2943,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123351656</v>
+        <v>123237971</v>
       </c>
       <c r="B24" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3091,37 +2954,49 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478475</v>
+        <v>478334</v>
       </c>
       <c r="R24" t="n">
-        <v>6790491</v>
+        <v>6790644</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3145,12 +3020,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Trumning från två håll i pågånde avverkningsområde vilket utförs av Mellanskog!</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3177,15 +3057,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123350545</v>
+        <v>123265474</v>
       </c>
       <c r="B25" t="n">
-        <v>57507</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3193,16 +3068,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3211,24 +3086,23 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478481</v>
+        <v>478414</v>
       </c>
       <c r="R25" t="n">
-        <v>6790519</v>
+        <v>6790720</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3252,12 +3126,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Troligt använt bo förra säsongen, inringat på bild.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3284,15 +3163,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123355658</v>
+        <v>123267825</v>
       </c>
       <c r="B26" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3300,34 +3174,38 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478318</v>
+        <v>478316</v>
       </c>
       <c r="R26" t="n">
-        <v>6790752</v>
+        <v>6790830</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3354,17 +3232,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Garnlav återfinns som rester efter avverkning i hela området, mer eller mindre.</t>
+          <t>Troligen hackspår efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3391,15 +3269,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123353192</v>
+        <v>123268735</v>
       </c>
       <c r="B27" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3425,19 +3298,23 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478402</v>
+        <v>478301</v>
       </c>
       <c r="R27" t="n">
-        <v>6790701</v>
+        <v>6790602</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3461,17 +3338,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Bo använt förra säsongen, fågelbo även 5 meter bredvid, enligt sista två bilder. Höjd på bohål ca 3 meter.</t>
+          <t>Troligen hackmärken från tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3498,15 +3375,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123353321</v>
+        <v>123353192</v>
       </c>
       <c r="B28" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3532,21 +3404,16 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478360</v>
+        <v>478402</v>
       </c>
       <c r="R28" t="n">
-        <v>6790647</v>
+        <v>6790701</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3579,6 +3446,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Bo använt förra säsongen, fågelbo även 5 meter bredvid, enligt sista två bilder. Höjd på bohål ca 3 meter.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3605,15 +3477,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123237971</v>
+        <v>123353321</v>
       </c>
       <c r="B29" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3638,32 +3505,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Skarpmyrarna, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478334</v>
+        <v>478360</v>
       </c>
       <c r="R29" t="n">
-        <v>6790644</v>
+        <v>6790647</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3687,17 +3547,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Trumning från två håll i pågånde avverkningsområde vilket utförs av Mellanskog!</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3721,6 +3576,215 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>123353670</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Skarpmyrarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>478339</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6790611</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Äldre hackspår på nedtryckt gran.</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>123220064</v>
+      </c>
+      <c r="B31" t="n">
+        <v>56522</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Skarpmyrarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>478304</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6790950</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48499-2024 artfynd.xlsx
+++ b/artfynd/A 48499-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123219384</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123220031</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123220381</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123222386</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1181,6 +1206,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123267228</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1287,6 +1317,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123267441</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1393,6 +1428,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123267612</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1499,6 +1539,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123268324</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1605,6 +1650,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123269013</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1711,6 +1761,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123269295</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1813,6 +1868,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123348213</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1910,6 +1970,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123351656</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2012,6 +2077,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123352253</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2114,6 +2184,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123355658</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2216,6 +2291,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123356603</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2318,6 +2398,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123347214</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2420,6 +2505,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123350545</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2527,6 +2617,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123351363</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2629,6 +2724,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123352363</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2731,6 +2831,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123222590</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2833,6 +2938,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123225119</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2940,6 +3050,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123225324</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3054,6 +3169,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123237971</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3160,6 +3280,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123265474</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3266,6 +3391,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123267825</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3372,6 +3502,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123268735</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3474,6 +3609,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123353192</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3576,6 +3716,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123353321</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3683,6 +3828,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123353670</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3785,8 +3935,45 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123220064</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>